--- a/research/traditional_assets/database/data/botswana/botswana_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07739569294365908</v>
+        <v>0.07726052241918303</v>
       </c>
       <c r="C2">
-        <v>97.10221581447604</v>
+        <v>96.26715687167194</v>
       </c>
       <c r="D2">
-        <v>66.20221581447603</v>
+        <v>66.34415687167194</v>
       </c>
       <c r="E2">
-        <v>-17.9</v>
+        <v>-16.923</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9769999999999999</v>
       </c>
       <c r="G2">
         <v>30.9</v>
@@ -1451,28 +1451,28 @@
         <v>15.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04914309999999999</v>
       </c>
       <c r="N2">
-        <v>15.8</v>
+        <v>15.7508569</v>
       </c>
       <c r="O2">
-        <v>3.476</v>
+        <v>3.465188518</v>
       </c>
       <c r="P2">
-        <v>12.324</v>
+        <v>12.285668382</v>
       </c>
       <c r="Q2">
-        <v>23.024</v>
+        <v>22.985668382</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07739569294365908</v>
+        <v>0.07764462870624549</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5369461886690254</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>321.5100390492257</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07726052241918303</v>
+        <v>0.07712535189470698</v>
       </c>
       <c r="C3">
-        <v>96.26715687167194</v>
+        <v>95.43270789495692</v>
       </c>
       <c r="D3">
-        <v>66.34415687167194</v>
+        <v>66.48670789495692</v>
       </c>
       <c r="E3">
-        <v>-16.923</v>
+        <v>-15.946</v>
       </c>
       <c r="F3">
-        <v>0.9769999999999999</v>
+        <v>1.954</v>
       </c>
       <c r="G3">
         <v>30.9</v>
@@ -1533,28 +1533,28 @@
         <v>15.8</v>
       </c>
       <c r="M3">
-        <v>0.04914309999999999</v>
+        <v>0.09828619999999998</v>
       </c>
       <c r="N3">
-        <v>15.7508569</v>
+        <v>15.7017138</v>
       </c>
       <c r="O3">
-        <v>3.465188518</v>
+        <v>3.454377036</v>
       </c>
       <c r="P3">
-        <v>12.285668382</v>
+        <v>12.247336764</v>
       </c>
       <c r="Q3">
-        <v>22.985668382</v>
+        <v>22.947336764</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07764462870624549</v>
+        <v>0.07789864479051734</v>
       </c>
       <c r="T3">
-        <v>0.5369461886690254</v>
+        <v>0.5412292647748445</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>321.5100390492257</v>
+        <v>160.7550195246129</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07712535189470698</v>
+        <v>0.07699018137023092</v>
       </c>
       <c r="C4">
-        <v>95.43270789495692</v>
+        <v>94.59887282462618</v>
       </c>
       <c r="D4">
-        <v>66.48670789495692</v>
+        <v>66.62987282462618</v>
       </c>
       <c r="E4">
-        <v>-15.946</v>
+        <v>-14.969</v>
       </c>
       <c r="F4">
-        <v>1.954</v>
+        <v>2.931</v>
       </c>
       <c r="G4">
         <v>30.9</v>
@@ -1615,28 +1615,28 @@
         <v>15.8</v>
       </c>
       <c r="M4">
-        <v>0.09828619999999998</v>
+        <v>0.1474293</v>
       </c>
       <c r="N4">
-        <v>15.7017138</v>
+        <v>15.6525707</v>
       </c>
       <c r="O4">
-        <v>3.454377036</v>
+        <v>3.443565554</v>
       </c>
       <c r="P4">
-        <v>12.247336764</v>
+        <v>12.209005146</v>
       </c>
       <c r="Q4">
-        <v>22.947336764</v>
+        <v>22.909005146</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07789864479051734</v>
+        <v>0.0781578983198257</v>
       </c>
       <c r="T4">
-        <v>0.5412292647748445</v>
+        <v>0.545600651728206</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>160.7550195246129</v>
+        <v>107.1700130164086</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07699018137023092</v>
+        <v>0.0768550108457549</v>
       </c>
       <c r="C5">
-        <v>94.59887282462618</v>
+        <v>93.76565563498646</v>
       </c>
       <c r="D5">
-        <v>66.62987282462618</v>
+        <v>66.77365563498645</v>
       </c>
       <c r="E5">
-        <v>-14.969</v>
+        <v>-13.992</v>
       </c>
       <c r="F5">
-        <v>2.931</v>
+        <v>3.907999999999999</v>
       </c>
       <c r="G5">
         <v>30.9</v>
@@ -1697,28 +1697,28 @@
         <v>15.8</v>
       </c>
       <c r="M5">
-        <v>0.1474293</v>
+        <v>0.1965724</v>
       </c>
       <c r="N5">
-        <v>15.6525707</v>
+        <v>15.6034276</v>
       </c>
       <c r="O5">
-        <v>3.443565554</v>
+        <v>3.432754072</v>
       </c>
       <c r="P5">
-        <v>12.209005146</v>
+        <v>12.170673528</v>
       </c>
       <c r="Q5">
-        <v>22.909005146</v>
+        <v>22.870673528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0781578983198257</v>
+        <v>0.07842255296432801</v>
       </c>
       <c r="T5">
-        <v>0.545600651728206</v>
+        <v>0.550063109243096</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>107.1700130164086</v>
+        <v>80.37750976230643</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0768550108457549</v>
+        <v>0.07671984032127883</v>
       </c>
       <c r="C6">
-        <v>93.76565563498646</v>
+        <v>92.93306033472395</v>
       </c>
       <c r="D6">
-        <v>66.77365563498645</v>
+        <v>66.91806033472395</v>
       </c>
       <c r="E6">
-        <v>-13.992</v>
+        <v>-13.015</v>
       </c>
       <c r="F6">
-        <v>3.907999999999999</v>
+        <v>4.885</v>
       </c>
       <c r="G6">
         <v>30.9</v>
@@ -1779,28 +1779,28 @@
         <v>15.8</v>
       </c>
       <c r="M6">
-        <v>0.1965724</v>
+        <v>0.2457155</v>
       </c>
       <c r="N6">
-        <v>15.6034276</v>
+        <v>15.5542845</v>
       </c>
       <c r="O6">
-        <v>3.432754072</v>
+        <v>3.42194259</v>
       </c>
       <c r="P6">
-        <v>12.170673528</v>
+        <v>12.13234191</v>
       </c>
       <c r="Q6">
-        <v>22.870673528</v>
+        <v>22.83234191</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07842255296432801</v>
+        <v>0.07869277928555668</v>
       </c>
       <c r="T6">
-        <v>0.550063109243096</v>
+        <v>0.5546195132319837</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>80.37750976230643</v>
+        <v>64.30200780984514</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07671984032127883</v>
+        <v>0.07658466979680277</v>
       </c>
       <c r="C7">
-        <v>92.93306033472395</v>
+        <v>92.10109096727666</v>
       </c>
       <c r="D7">
-        <v>66.91806033472395</v>
+        <v>67.06309096727665</v>
       </c>
       <c r="E7">
-        <v>-13.015</v>
+        <v>-12.038</v>
       </c>
       <c r="F7">
-        <v>4.885</v>
+        <v>5.862</v>
       </c>
       <c r="G7">
         <v>30.9</v>
@@ -1861,28 +1861,28 @@
         <v>15.8</v>
       </c>
       <c r="M7">
-        <v>0.2457155</v>
+        <v>0.2948586</v>
       </c>
       <c r="N7">
-        <v>15.5542845</v>
+        <v>15.5051414</v>
       </c>
       <c r="O7">
-        <v>3.42194259</v>
+        <v>3.411131108</v>
       </c>
       <c r="P7">
-        <v>12.13234191</v>
+        <v>12.094010292</v>
       </c>
       <c r="Q7">
-        <v>22.83234191</v>
+        <v>22.794010292</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07869277928555668</v>
+        <v>0.07896875510298168</v>
       </c>
       <c r="T7">
-        <v>0.5546195132319837</v>
+        <v>0.5592728619865922</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.30200780984514</v>
+        <v>53.58500650820428</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07658466979680277</v>
+        <v>0.07644949927232672</v>
       </c>
       <c r="C8">
-        <v>92.10109096727666</v>
+        <v>91.26975161121186</v>
       </c>
       <c r="D8">
-        <v>67.06309096727665</v>
+        <v>67.20875161121185</v>
       </c>
       <c r="E8">
-        <v>-12.038</v>
+        <v>-11.061</v>
       </c>
       <c r="F8">
-        <v>5.861999999999999</v>
+        <v>6.838999999999999</v>
       </c>
       <c r="G8">
         <v>30.9</v>
@@ -1943,28 +1943,28 @@
         <v>15.8</v>
       </c>
       <c r="M8">
-        <v>0.2948586</v>
+        <v>0.3440016999999999</v>
       </c>
       <c r="N8">
-        <v>15.5051414</v>
+        <v>15.4559983</v>
       </c>
       <c r="O8">
-        <v>3.411131108</v>
+        <v>3.400319626</v>
       </c>
       <c r="P8">
-        <v>12.094010292</v>
+        <v>12.055678674</v>
       </c>
       <c r="Q8">
-        <v>22.794010292</v>
+        <v>22.755678674</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07896875510298168</v>
+        <v>0.07925066588422229</v>
       </c>
       <c r="T8">
-        <v>0.5592728619865922</v>
+        <v>0.5640262827574289</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.58500650820428</v>
+        <v>45.93000557846082</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07644949927232675</v>
+        <v>0.07631432874785068</v>
       </c>
       <c r="C9">
-        <v>91.2697516112118</v>
+        <v>90.43904638060846</v>
       </c>
       <c r="D9">
-        <v>67.20875161121181</v>
+        <v>67.35504638060847</v>
       </c>
       <c r="E9">
-        <v>-11.061</v>
+        <v>-10.084</v>
       </c>
       <c r="F9">
-        <v>6.839</v>
+        <v>7.815999999999999</v>
       </c>
       <c r="G9">
         <v>30.9</v>
@@ -2025,28 +2025,28 @@
         <v>15.8</v>
       </c>
       <c r="M9">
-        <v>0.3440017</v>
+        <v>0.3931447999999999</v>
       </c>
       <c r="N9">
-        <v>15.4559983</v>
+        <v>15.4068552</v>
       </c>
       <c r="O9">
-        <v>3.400319626</v>
+        <v>3.389508144</v>
       </c>
       <c r="P9">
-        <v>12.055678674</v>
+        <v>12.017347056</v>
       </c>
       <c r="Q9">
-        <v>22.755678674</v>
+        <v>22.717347056</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0792506658842223</v>
+        <v>0.07953870516070727</v>
       </c>
       <c r="T9">
-        <v>0.5640262827574291</v>
+        <v>0.5688830387624144</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.93000557846081</v>
+        <v>40.18875488115322</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07631432874785068</v>
+        <v>0.07617915822337464</v>
       </c>
       <c r="C10">
-        <v>90.43904638060846</v>
+        <v>89.60897942544449</v>
       </c>
       <c r="D10">
-        <v>67.35504638060847</v>
+        <v>67.50197942544449</v>
       </c>
       <c r="E10">
-        <v>-10.084</v>
+        <v>-9.106999999999999</v>
       </c>
       <c r="F10">
-        <v>7.815999999999999</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="G10">
         <v>30.9</v>
@@ -2107,28 +2107,28 @@
         <v>15.8</v>
       </c>
       <c r="M10">
-        <v>0.3931447999999999</v>
+        <v>0.4422879</v>
       </c>
       <c r="N10">
-        <v>15.4068552</v>
+        <v>15.3577121</v>
       </c>
       <c r="O10">
-        <v>3.389508144</v>
+        <v>3.378696662</v>
       </c>
       <c r="P10">
-        <v>12.017347056</v>
+        <v>11.979015438</v>
       </c>
       <c r="Q10">
-        <v>22.717347056</v>
+        <v>22.679015438</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07953870516070727</v>
+        <v>0.07983307497074135</v>
       </c>
       <c r="T10">
-        <v>0.5688830387624144</v>
+        <v>0.5738465366576193</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.18875488115322</v>
+        <v>35.72333767213618</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07617915822337464</v>
+        <v>0.07604398769889859</v>
       </c>
       <c r="C11">
-        <v>89.60897942544449</v>
+        <v>88.77955493198918</v>
       </c>
       <c r="D11">
-        <v>67.50197942544449</v>
+        <v>67.64955493198919</v>
       </c>
       <c r="E11">
-        <v>-9.106999999999999</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="F11">
-        <v>8.792999999999999</v>
+        <v>9.769999999999998</v>
       </c>
       <c r="G11">
         <v>30.9</v>
@@ -2189,28 +2189,28 @@
         <v>15.8</v>
       </c>
       <c r="M11">
-        <v>0.4422879</v>
+        <v>0.4914309999999998</v>
       </c>
       <c r="N11">
-        <v>15.3577121</v>
+        <v>15.308569</v>
       </c>
       <c r="O11">
-        <v>3.378696662</v>
+        <v>3.36788518</v>
       </c>
       <c r="P11">
-        <v>11.979015438</v>
+        <v>11.94068382</v>
       </c>
       <c r="Q11">
-        <v>22.679015438</v>
+        <v>22.64068382</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07983307497074135</v>
+        <v>0.08013398633210954</v>
       </c>
       <c r="T11">
-        <v>0.5738465366576193</v>
+        <v>0.578920334506051</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.72333767213618</v>
+        <v>32.15100390492258</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07604398769889859</v>
+        <v>0.07590881717442254</v>
       </c>
       <c r="C12">
-        <v>88.77955493198918</v>
+        <v>87.95077712320078</v>
       </c>
       <c r="D12">
-        <v>67.64955493198919</v>
+        <v>67.79777712320077</v>
       </c>
       <c r="E12">
-        <v>-8.129999999999999</v>
+        <v>-7.153</v>
       </c>
       <c r="F12">
-        <v>9.77</v>
+        <v>10.747</v>
       </c>
       <c r="G12">
         <v>30.9</v>
@@ -2271,28 +2271,28 @@
         <v>15.8</v>
       </c>
       <c r="M12">
-        <v>0.491431</v>
+        <v>0.5405740999999998</v>
       </c>
       <c r="N12">
-        <v>15.308569</v>
+        <v>15.2594259</v>
       </c>
       <c r="O12">
-        <v>3.36788518</v>
+        <v>3.357073698</v>
       </c>
       <c r="P12">
-        <v>11.94068382</v>
+        <v>11.902352202</v>
       </c>
       <c r="Q12">
-        <v>22.64068382</v>
+        <v>22.602352202</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08013398633210954</v>
+        <v>0.08044165974654217</v>
       </c>
       <c r="T12">
-        <v>0.578920334506051</v>
+        <v>0.5841081502836609</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.15100390492257</v>
+        <v>29.22818536811143</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07590881717442254</v>
+        <v>0.07577364664994649</v>
       </c>
       <c r="C13">
-        <v>87.95077712320078</v>
+        <v>87.12265025912932</v>
       </c>
       <c r="D13">
-        <v>67.79777712320077</v>
+        <v>67.94665025912933</v>
       </c>
       <c r="E13">
-        <v>-7.153</v>
+        <v>-6.176</v>
       </c>
       <c r="F13">
-        <v>10.747</v>
+        <v>11.724</v>
       </c>
       <c r="G13">
         <v>30.9</v>
@@ -2353,28 +2353,28 @@
         <v>15.8</v>
       </c>
       <c r="M13">
-        <v>0.5405740999999998</v>
+        <v>0.5897171999999999</v>
       </c>
       <c r="N13">
-        <v>15.2594259</v>
+        <v>15.2102828</v>
       </c>
       <c r="O13">
-        <v>3.357073698</v>
+        <v>3.346262216</v>
       </c>
       <c r="P13">
-        <v>11.902352202</v>
+        <v>11.864020584</v>
       </c>
       <c r="Q13">
-        <v>22.602352202</v>
+        <v>22.564020584</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08044165974654217</v>
+        <v>0.08075632573857555</v>
       </c>
       <c r="T13">
-        <v>0.5841081502836609</v>
+        <v>0.5894138709653074</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.22818536811143</v>
+        <v>26.79250325410214</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07577364664994649</v>
+        <v>0.07563847612547042</v>
       </c>
       <c r="C14">
-        <v>87.12265025912932</v>
+        <v>86.2951786373248</v>
       </c>
       <c r="D14">
-        <v>67.94665025912933</v>
+        <v>68.0961786373248</v>
       </c>
       <c r="E14">
-        <v>-6.176</v>
+        <v>-5.199</v>
       </c>
       <c r="F14">
-        <v>11.724</v>
+        <v>12.701</v>
       </c>
       <c r="G14">
         <v>30.9</v>
@@ -2435,28 +2435,28 @@
         <v>15.8</v>
       </c>
       <c r="M14">
-        <v>0.5897171999999999</v>
+        <v>0.6388602999999999</v>
       </c>
       <c r="N14">
-        <v>15.2102828</v>
+        <v>15.1611397</v>
       </c>
       <c r="O14">
-        <v>3.346262216</v>
+        <v>3.335450734</v>
       </c>
       <c r="P14">
-        <v>11.864020584</v>
+        <v>11.825688966</v>
       </c>
       <c r="Q14">
-        <v>22.564020584</v>
+        <v>22.525688966</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08075632573857555</v>
+        <v>0.08107822543157521</v>
       </c>
       <c r="T14">
-        <v>0.5894138709653074</v>
+        <v>0.5948415622373364</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.79250325410214</v>
+        <v>24.73154146532505</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07563847612547042</v>
+        <v>0.07550330560099439</v>
       </c>
       <c r="C15">
-        <v>86.2951786373248</v>
+        <v>85.46836659325055</v>
       </c>
       <c r="D15">
-        <v>68.0961786373248</v>
+        <v>68.24636659325054</v>
       </c>
       <c r="E15">
-        <v>-5.199</v>
+        <v>-4.222</v>
       </c>
       <c r="F15">
-        <v>12.701</v>
+        <v>13.678</v>
       </c>
       <c r="G15">
         <v>30.9</v>
@@ -2517,28 +2517,28 @@
         <v>15.8</v>
       </c>
       <c r="M15">
-        <v>0.6388602999999999</v>
+        <v>0.6880033999999999</v>
       </c>
       <c r="N15">
-        <v>15.1611397</v>
+        <v>15.1119966</v>
       </c>
       <c r="O15">
-        <v>3.335450734</v>
+        <v>3.324639252</v>
       </c>
       <c r="P15">
-        <v>11.825688966</v>
+        <v>11.787357348</v>
       </c>
       <c r="Q15">
-        <v>22.525688966</v>
+        <v>22.487357348</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08107822543157521</v>
+        <v>0.08140761116394696</v>
       </c>
       <c r="T15">
-        <v>0.5948415622373364</v>
+        <v>0.6003954788877849</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.73154146532505</v>
+        <v>22.96500278923041</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07550330560099439</v>
+        <v>0.07536813507651834</v>
       </c>
       <c r="C16">
-        <v>85.46836659325055</v>
+        <v>84.64221850070248</v>
       </c>
       <c r="D16">
-        <v>68.24636659325054</v>
+        <v>68.39721850070249</v>
       </c>
       <c r="E16">
-        <v>-4.222</v>
+        <v>-3.244999999999997</v>
       </c>
       <c r="F16">
-        <v>13.678</v>
+        <v>14.655</v>
       </c>
       <c r="G16">
         <v>30.9</v>
@@ -2599,28 +2599,28 @@
         <v>15.8</v>
       </c>
       <c r="M16">
-        <v>0.6880033999999999</v>
+        <v>0.7371465</v>
       </c>
       <c r="N16">
-        <v>15.1119966</v>
+        <v>15.0628535</v>
       </c>
       <c r="O16">
-        <v>3.324639252</v>
+        <v>3.31382777</v>
       </c>
       <c r="P16">
-        <v>11.787357348</v>
+        <v>11.74902573</v>
       </c>
       <c r="Q16">
-        <v>22.487357348</v>
+        <v>22.44902573</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08140761116394696</v>
+        <v>0.0817447471488451</v>
       </c>
       <c r="T16">
-        <v>0.6003954788877849</v>
+        <v>0.6060800759300086</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.96500278923041</v>
+        <v>21.43400260328171</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07536813507651834</v>
+        <v>0.07523296455204229</v>
       </c>
       <c r="C17">
-        <v>84.64221850070248</v>
+        <v>83.81673877223355</v>
       </c>
       <c r="D17">
-        <v>68.39721850070249</v>
+        <v>68.54873877223355</v>
       </c>
       <c r="E17">
-        <v>-3.245000000000001</v>
+        <v>-2.268000000000001</v>
       </c>
       <c r="F17">
-        <v>14.655</v>
+        <v>15.632</v>
       </c>
       <c r="G17">
         <v>30.9</v>
@@ -2681,28 +2681,28 @@
         <v>15.8</v>
       </c>
       <c r="M17">
-        <v>0.7371464999999998</v>
+        <v>0.7862895999999998</v>
       </c>
       <c r="N17">
-        <v>15.0628535</v>
+        <v>15.0137104</v>
       </c>
       <c r="O17">
-        <v>3.31382777</v>
+        <v>3.303016288</v>
       </c>
       <c r="P17">
-        <v>11.74902573</v>
+        <v>11.710694112</v>
       </c>
       <c r="Q17">
-        <v>22.44902573</v>
+        <v>22.410694112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0817447471488451</v>
+        <v>0.08208991018100273</v>
       </c>
       <c r="T17">
-        <v>0.6060800759300086</v>
+        <v>0.6119000205208567</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.43400260328172</v>
+        <v>20.09437744057661</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07523296455204229</v>
+        <v>0.07509779402756624</v>
       </c>
       <c r="C18">
-        <v>83.81673877223355</v>
+        <v>82.99193185958389</v>
       </c>
       <c r="D18">
-        <v>68.54873877223355</v>
+        <v>68.70093185958389</v>
       </c>
       <c r="E18">
-        <v>-2.268000000000001</v>
+        <v>-1.291</v>
       </c>
       <c r="F18">
-        <v>15.632</v>
+        <v>16.609</v>
       </c>
       <c r="G18">
         <v>30.9</v>
@@ -2763,28 +2763,28 @@
         <v>15.8</v>
       </c>
       <c r="M18">
-        <v>0.7862895999999998</v>
+        <v>0.8354326999999999</v>
       </c>
       <c r="N18">
-        <v>15.0137104</v>
+        <v>14.9645673</v>
       </c>
       <c r="O18">
-        <v>3.303016288</v>
+        <v>3.292204806</v>
       </c>
       <c r="P18">
-        <v>11.710694112</v>
+        <v>11.672362494</v>
       </c>
       <c r="Q18">
-        <v>22.410694112</v>
+        <v>22.372362494</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08208991018100273</v>
+        <v>0.08244339039465812</v>
       </c>
       <c r="T18">
-        <v>0.6119000205208567</v>
+        <v>0.6178602047403999</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.09437744057661</v>
+        <v>18.91235523818975</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07509779402756624</v>
+        <v>0.07496262350309017</v>
       </c>
       <c r="C19">
-        <v>82.99193185958389</v>
+        <v>82.16780225411715</v>
       </c>
       <c r="D19">
-        <v>68.70093185958389</v>
+        <v>68.85380225411714</v>
       </c>
       <c r="E19">
-        <v>-1.291</v>
+        <v>-0.3140000000000001</v>
       </c>
       <c r="F19">
-        <v>16.609</v>
+        <v>17.586</v>
       </c>
       <c r="G19">
         <v>30.9</v>
@@ -2845,28 +2845,28 @@
         <v>15.8</v>
       </c>
       <c r="M19">
-        <v>0.8354326999999999</v>
+        <v>0.8845757999999999</v>
       </c>
       <c r="N19">
-        <v>14.9645673</v>
+        <v>14.9154242</v>
       </c>
       <c r="O19">
-        <v>3.292204806</v>
+        <v>3.281393324</v>
       </c>
       <c r="P19">
-        <v>11.672362494</v>
+        <v>11.634030876</v>
       </c>
       <c r="Q19">
-        <v>22.372362494</v>
+        <v>22.334030876</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08244339039465812</v>
+        <v>0.08280549207693924</v>
       </c>
       <c r="T19">
-        <v>0.6178602047403999</v>
+        <v>0.6239657593067612</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.91235523818975</v>
+        <v>17.86166883606809</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07496262350309019</v>
+        <v>0.07482745297861414</v>
       </c>
       <c r="C20">
-        <v>82.16780225411712</v>
+        <v>81.34435448726181</v>
       </c>
       <c r="D20">
-        <v>68.85380225411711</v>
+        <v>69.00735448726182</v>
       </c>
       <c r="E20">
-        <v>-0.3140000000000001</v>
+        <v>0.6630000000000003</v>
       </c>
       <c r="F20">
-        <v>17.586</v>
+        <v>18.563</v>
       </c>
       <c r="G20">
         <v>30.9</v>
@@ -2927,28 +2927,28 @@
         <v>15.8</v>
       </c>
       <c r="M20">
-        <v>0.8845757999999999</v>
+        <v>0.9337188999999999</v>
       </c>
       <c r="N20">
-        <v>14.9154242</v>
+        <v>14.8662811</v>
       </c>
       <c r="O20">
-        <v>3.281393324</v>
+        <v>3.270581842</v>
       </c>
       <c r="P20">
-        <v>11.634030876</v>
+        <v>11.595699258</v>
       </c>
       <c r="Q20">
-        <v>22.334030876</v>
+        <v>22.295699258</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08280549207693924</v>
+        <v>0.08317653454149893</v>
       </c>
       <c r="T20">
-        <v>0.6239657593067611</v>
+        <v>0.6302220683068598</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.86166883606809</v>
+        <v>16.92158100259083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07482745297861414</v>
+        <v>0.07469228245413809</v>
       </c>
       <c r="C21">
-        <v>81.34435448726181</v>
+        <v>80.52159313095953</v>
       </c>
       <c r="D21">
-        <v>69.00735448726182</v>
+        <v>69.16159313095953</v>
       </c>
       <c r="E21">
-        <v>0.6630000000000003</v>
+        <v>1.640000000000001</v>
       </c>
       <c r="F21">
-        <v>18.563</v>
+        <v>19.54</v>
       </c>
       <c r="G21">
         <v>30.9</v>
@@ -3009,28 +3009,28 @@
         <v>15.8</v>
       </c>
       <c r="M21">
-        <v>0.9337188999999999</v>
+        <v>0.9828619999999999</v>
       </c>
       <c r="N21">
-        <v>14.8662811</v>
+        <v>14.817138</v>
       </c>
       <c r="O21">
-        <v>3.270581842</v>
+        <v>3.25977036</v>
       </c>
       <c r="P21">
-        <v>11.595699258</v>
+        <v>11.55736764</v>
       </c>
       <c r="Q21">
-        <v>22.295699258</v>
+        <v>22.25736764</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08317653454149893</v>
+        <v>0.0835568530676726</v>
       </c>
       <c r="T21">
-        <v>0.6302220683068598</v>
+        <v>0.6366347850319609</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.92158100259083</v>
+        <v>16.07550195246128</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07469228245413809</v>
+        <v>0.07455711192966204</v>
       </c>
       <c r="C22">
-        <v>80.52159313095953</v>
+        <v>79.69952279811835</v>
       </c>
       <c r="D22">
-        <v>69.16159313095953</v>
+        <v>69.31652279811834</v>
       </c>
       <c r="E22">
-        <v>1.640000000000001</v>
+        <v>2.617000000000001</v>
       </c>
       <c r="F22">
-        <v>19.54</v>
+        <v>20.517</v>
       </c>
       <c r="G22">
         <v>30.9</v>
@@ -3091,28 +3091,28 @@
         <v>15.8</v>
       </c>
       <c r="M22">
-        <v>0.9828619999999999</v>
+        <v>1.0320051</v>
       </c>
       <c r="N22">
-        <v>14.817138</v>
+        <v>14.7679949</v>
       </c>
       <c r="O22">
-        <v>3.25977036</v>
+        <v>3.248958878</v>
       </c>
       <c r="P22">
-        <v>11.55736764</v>
+        <v>11.519036022</v>
       </c>
       <c r="Q22">
-        <v>22.25736764</v>
+        <v>22.219036022</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0835568530676726</v>
+        <v>0.0839467999109646</v>
       </c>
       <c r="T22">
-        <v>0.6366347850319609</v>
+        <v>0.6432098490159254</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.07550195246128</v>
+        <v>15.31000185948694</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07455711192966202</v>
+        <v>0.07442194140518597</v>
       </c>
       <c r="C23">
-        <v>79.69952279811835</v>
+        <v>78.87814814307293</v>
       </c>
       <c r="D23">
-        <v>69.31652279811836</v>
+        <v>69.47214814307294</v>
       </c>
       <c r="E23">
-        <v>2.616999999999997</v>
+        <v>3.593999999999998</v>
       </c>
       <c r="F23">
-        <v>20.517</v>
+        <v>21.494</v>
       </c>
       <c r="G23">
         <v>30.9</v>
@@ -3173,28 +3173,28 @@
         <v>15.8</v>
       </c>
       <c r="M23">
-        <v>1.0320051</v>
+        <v>1.0811482</v>
       </c>
       <c r="N23">
-        <v>14.7679949</v>
+        <v>14.7188518</v>
       </c>
       <c r="O23">
-        <v>3.248958878</v>
+        <v>3.238147396</v>
       </c>
       <c r="P23">
-        <v>11.519036022</v>
+        <v>11.480704404</v>
       </c>
       <c r="Q23">
-        <v>22.219036022</v>
+        <v>22.180704404</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0839467999109646</v>
+        <v>0.08434674539126408</v>
       </c>
       <c r="T23">
-        <v>0.6432098490159253</v>
+        <v>0.6499535043840939</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.31000185948694</v>
+        <v>14.61409268405572</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07442194140518597</v>
+        <v>0.07428677088070994</v>
       </c>
       <c r="C24">
-        <v>78.87814814307293</v>
+        <v>78.05747386205053</v>
       </c>
       <c r="D24">
-        <v>69.47214814307294</v>
+        <v>69.62847386205053</v>
       </c>
       <c r="E24">
-        <v>3.593999999999998</v>
+        <v>4.571000000000002</v>
       </c>
       <c r="F24">
-        <v>21.494</v>
+        <v>22.471</v>
       </c>
       <c r="G24">
         <v>30.9</v>
@@ -3255,28 +3255,28 @@
         <v>15.8</v>
       </c>
       <c r="M24">
-        <v>1.0811482</v>
+        <v>1.1302913</v>
       </c>
       <c r="N24">
-        <v>14.7188518</v>
+        <v>14.6697087</v>
       </c>
       <c r="O24">
-        <v>3.238147396</v>
+        <v>3.227335914</v>
       </c>
       <c r="P24">
-        <v>11.480704404</v>
+        <v>11.442372786</v>
       </c>
       <c r="Q24">
-        <v>22.180704404</v>
+        <v>22.142372786</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08434674539126408</v>
+        <v>0.08475707906585705</v>
       </c>
       <c r="T24">
-        <v>0.6499535043840939</v>
+        <v>0.6568723196319554</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.61409268405572</v>
+        <v>13.97869734996633</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07428677088070994</v>
+        <v>0.07415160035623389</v>
       </c>
       <c r="C25">
-        <v>78.05747386205053</v>
+        <v>77.23750469364339</v>
       </c>
       <c r="D25">
-        <v>69.62847386205053</v>
+        <v>69.78550469364339</v>
       </c>
       <c r="E25">
-        <v>4.571000000000002</v>
+        <v>5.548000000000002</v>
       </c>
       <c r="F25">
-        <v>22.471</v>
+        <v>23.448</v>
       </c>
       <c r="G25">
         <v>30.9</v>
@@ -3337,28 +3337,28 @@
         <v>15.8</v>
       </c>
       <c r="M25">
-        <v>1.1302913</v>
+        <v>1.1794344</v>
       </c>
       <c r="N25">
-        <v>14.6697087</v>
+        <v>14.6205656</v>
       </c>
       <c r="O25">
-        <v>3.227335914</v>
+        <v>3.216524432</v>
       </c>
       <c r="P25">
-        <v>11.442372786</v>
+        <v>11.404041168</v>
       </c>
       <c r="Q25">
-        <v>22.142372786</v>
+        <v>22.104041168</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08475707906585705</v>
+        <v>0.08517821099504458</v>
       </c>
       <c r="T25">
-        <v>0.6568723196319554</v>
+        <v>0.6639732089652868</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.97869734996633</v>
+        <v>13.39625162705107</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07415160035623389</v>
+        <v>0.07430892983175784</v>
       </c>
       <c r="C26">
-        <v>77.2375046936434</v>
+        <v>76.077798675446</v>
       </c>
       <c r="D26">
-        <v>69.78550469364339</v>
+        <v>69.602798675446</v>
       </c>
       <c r="E26">
-        <v>5.547999999999998</v>
+        <v>6.524999999999999</v>
       </c>
       <c r="F26">
-        <v>23.448</v>
+        <v>24.425</v>
       </c>
       <c r="G26">
         <v>30.9</v>
@@ -3419,45 +3419,45 @@
         <v>15.8</v>
       </c>
       <c r="M26">
-        <v>1.1794344</v>
+        <v>1.265215</v>
       </c>
       <c r="N26">
-        <v>14.6205656</v>
+        <v>14.534785</v>
       </c>
       <c r="O26">
-        <v>3.216524432</v>
+        <v>3.1976527</v>
       </c>
       <c r="P26">
-        <v>11.404041168</v>
+        <v>11.3371323</v>
       </c>
       <c r="Q26">
-        <v>22.104041168</v>
+        <v>22.0371323</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08517821099504458</v>
+        <v>0.08561057310901045</v>
       </c>
       <c r="T26">
-        <v>0.6639732089652868</v>
+        <v>0.671263455347507</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.39625162705107</v>
+        <v>12.48799611133286</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07430892983175784</v>
+        <v>0.07418545930728179</v>
       </c>
       <c r="C27">
-        <v>76.077798675446</v>
+        <v>75.24410348857027</v>
       </c>
       <c r="D27">
-        <v>69.602798675446</v>
+        <v>69.74610348857027</v>
       </c>
       <c r="E27">
-        <v>6.524999999999999</v>
+        <v>7.501999999999999</v>
       </c>
       <c r="F27">
-        <v>24.425</v>
+        <v>25.402</v>
       </c>
       <c r="G27">
         <v>30.9</v>
@@ -3501,28 +3501,28 @@
         <v>15.8</v>
       </c>
       <c r="M27">
-        <v>1.265215</v>
+        <v>1.3158236</v>
       </c>
       <c r="N27">
-        <v>14.534785</v>
+        <v>14.4841764</v>
       </c>
       <c r="O27">
-        <v>3.1976527</v>
+        <v>3.186518808</v>
       </c>
       <c r="P27">
-        <v>11.3371323</v>
+        <v>11.297657592</v>
       </c>
       <c r="Q27">
-        <v>22.0371323</v>
+        <v>21.997657592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08561057310901045</v>
+        <v>0.08605462068551592</v>
       </c>
       <c r="T27">
-        <v>0.671263455347507</v>
+        <v>0.6787507354157332</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.48799611133286</v>
+        <v>12.00768856858929</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07418545930728179</v>
+        <v>0.07406198878280575</v>
       </c>
       <c r="C28">
-        <v>75.24410348857027</v>
+        <v>74.41099961811</v>
       </c>
       <c r="D28">
-        <v>69.74610348857027</v>
+        <v>69.88999961810998</v>
       </c>
       <c r="E28">
-        <v>7.501999999999999</v>
+        <v>8.478999999999999</v>
       </c>
       <c r="F28">
-        <v>25.402</v>
+        <v>26.379</v>
       </c>
       <c r="G28">
         <v>30.9</v>
@@ -3583,28 +3583,28 @@
         <v>15.8</v>
       </c>
       <c r="M28">
-        <v>1.3158236</v>
+        <v>1.3664322</v>
       </c>
       <c r="N28">
-        <v>14.4841764</v>
+        <v>14.4335678</v>
       </c>
       <c r="O28">
-        <v>3.186518808</v>
+        <v>3.175384916</v>
       </c>
       <c r="P28">
-        <v>11.297657592</v>
+        <v>11.258182884</v>
       </c>
       <c r="Q28">
-        <v>21.997657592</v>
+        <v>21.958182884</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08605462068551592</v>
+        <v>0.08651083394904896</v>
       </c>
       <c r="T28">
-        <v>0.6787507354157332</v>
+        <v>0.6864431464447326</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.00768856858929</v>
+        <v>11.56295936234524</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07406198878280575</v>
+        <v>0.07393851825832969</v>
       </c>
       <c r="C29">
-        <v>74.41099961811</v>
+        <v>73.57849073154125</v>
       </c>
       <c r="D29">
-        <v>69.88999961810998</v>
+        <v>70.03449073154124</v>
       </c>
       <c r="E29">
-        <v>8.478999999999999</v>
+        <v>9.456</v>
       </c>
       <c r="F29">
-        <v>26.379</v>
+        <v>27.356</v>
       </c>
       <c r="G29">
         <v>30.9</v>
@@ -3665,28 +3665,28 @@
         <v>15.8</v>
       </c>
       <c r="M29">
-        <v>1.3664322</v>
+        <v>1.4170408</v>
       </c>
       <c r="N29">
-        <v>14.4335678</v>
+        <v>14.3829592</v>
       </c>
       <c r="O29">
-        <v>3.175384916</v>
+        <v>3.164251024</v>
       </c>
       <c r="P29">
-        <v>11.258182884</v>
+        <v>11.218708176</v>
       </c>
       <c r="Q29">
-        <v>21.958182884</v>
+        <v>21.918708176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08651083394904896</v>
+        <v>0.08697971980323568</v>
       </c>
       <c r="T29">
-        <v>0.6864431464447326</v>
+        <v>0.694349235557871</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.56295936234524</v>
+        <v>11.14999652797577</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07393851825832969</v>
+        <v>0.07381504773385363</v>
       </c>
       <c r="C30">
-        <v>73.57849073154125</v>
+        <v>72.74658052673161</v>
       </c>
       <c r="D30">
-        <v>70.03449073154124</v>
+        <v>70.17958052673161</v>
       </c>
       <c r="E30">
-        <v>9.456</v>
+        <v>10.433</v>
       </c>
       <c r="F30">
-        <v>27.356</v>
+        <v>28.333</v>
       </c>
       <c r="G30">
         <v>30.9</v>
@@ -3747,28 +3747,28 @@
         <v>15.8</v>
       </c>
       <c r="M30">
-        <v>1.4170408</v>
+        <v>1.4676494</v>
       </c>
       <c r="N30">
-        <v>14.3829592</v>
+        <v>14.3323506</v>
       </c>
       <c r="O30">
-        <v>3.164251024</v>
+        <v>3.153117132</v>
       </c>
       <c r="P30">
-        <v>11.218708176</v>
+        <v>11.179233468</v>
       </c>
       <c r="Q30">
-        <v>21.918708176</v>
+        <v>21.879233468</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08697971980323568</v>
+        <v>0.087461813709653</v>
       </c>
       <c r="T30">
-        <v>0.694349235557871</v>
+        <v>0.7024780314065907</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.14999652797577</v>
+        <v>10.76551388908005</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07381504773385363</v>
+        <v>0.07369157720937758</v>
       </c>
       <c r="C31">
-        <v>72.74658052673161</v>
+        <v>71.9152727322556</v>
       </c>
       <c r="D31">
-        <v>70.17958052673161</v>
+        <v>70.3252727322556</v>
       </c>
       <c r="E31">
-        <v>10.433</v>
+        <v>11.41</v>
       </c>
       <c r="F31">
-        <v>28.33299999999999</v>
+        <v>29.31</v>
       </c>
       <c r="G31">
         <v>30.9</v>
@@ -3829,28 +3829,28 @@
         <v>15.8</v>
       </c>
       <c r="M31">
-        <v>1.4676494</v>
+        <v>1.518258</v>
       </c>
       <c r="N31">
-        <v>14.3323506</v>
+        <v>14.281742</v>
       </c>
       <c r="O31">
-        <v>3.153117132</v>
+        <v>3.141983240000001</v>
       </c>
       <c r="P31">
-        <v>11.179233468</v>
+        <v>11.13975876</v>
       </c>
       <c r="Q31">
-        <v>21.879233468</v>
+        <v>21.83975876</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.087461813709653</v>
+        <v>0.08795768172768226</v>
       </c>
       <c r="T31">
-        <v>0.7024780314065907</v>
+        <v>0.7108390785652737</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.76551388908005</v>
+        <v>10.40666342611072</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07369157720937758</v>
+        <v>0.07356810668490152</v>
       </c>
       <c r="C32">
-        <v>71.9152727322556</v>
+        <v>71.08457110771418</v>
       </c>
       <c r="D32">
-        <v>70.3252727322556</v>
+        <v>70.47157110771418</v>
       </c>
       <c r="E32">
-        <v>11.41</v>
+        <v>12.387</v>
       </c>
       <c r="F32">
-        <v>29.31</v>
+        <v>30.287</v>
       </c>
       <c r="G32">
         <v>30.9</v>
@@ -3911,28 +3911,28 @@
         <v>15.8</v>
       </c>
       <c r="M32">
-        <v>1.518258</v>
+        <v>1.5688666</v>
       </c>
       <c r="N32">
-        <v>14.281742</v>
+        <v>14.2311334</v>
       </c>
       <c r="O32">
-        <v>3.141983240000001</v>
+        <v>3.130849348</v>
       </c>
       <c r="P32">
-        <v>11.13975876</v>
+        <v>11.100284052</v>
       </c>
       <c r="Q32">
-        <v>21.83975876</v>
+        <v>21.800284052</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08795768172768226</v>
+        <v>0.08846792273174135</v>
       </c>
       <c r="T32">
-        <v>0.7108390785652737</v>
+        <v>0.7194424749169622</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.40666342611072</v>
+        <v>10.0709646059136</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07356810668490152</v>
+        <v>0.07386895616042549</v>
       </c>
       <c r="C33">
-        <v>71.08457110771418</v>
+        <v>69.75215904658462</v>
       </c>
       <c r="D33">
-        <v>70.47157110771418</v>
+        <v>70.11615904658463</v>
       </c>
       <c r="E33">
-        <v>12.387</v>
+        <v>13.364</v>
       </c>
       <c r="F33">
-        <v>30.287</v>
+        <v>31.264</v>
       </c>
       <c r="G33">
         <v>30.9</v>
@@ -3993,45 +3993,45 @@
         <v>15.8</v>
       </c>
       <c r="M33">
-        <v>1.5688666</v>
+        <v>1.672624</v>
       </c>
       <c r="N33">
-        <v>14.2311334</v>
+        <v>14.127376</v>
       </c>
       <c r="O33">
-        <v>3.130849348</v>
+        <v>3.108022720000001</v>
       </c>
       <c r="P33">
-        <v>11.100284052</v>
+        <v>11.01935328</v>
       </c>
       <c r="Q33">
-        <v>21.800284052</v>
+        <v>21.71935328</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08846792273174135</v>
+        <v>0.08899317082415513</v>
       </c>
       <c r="T33">
-        <v>0.7194424749169622</v>
+        <v>0.7282989123378181</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.0709646059136</v>
+        <v>9.44623537627106</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07386895616042549</v>
+        <v>0.07375874563594943</v>
       </c>
       <c r="C34">
-        <v>69.75215904658462</v>
+        <v>68.90494068452848</v>
       </c>
       <c r="D34">
-        <v>70.11615904658463</v>
+        <v>70.24594068452849</v>
       </c>
       <c r="E34">
-        <v>13.364</v>
+        <v>14.341</v>
       </c>
       <c r="F34">
-        <v>31.264</v>
+        <v>32.241</v>
       </c>
       <c r="G34">
         <v>30.9</v>
@@ -4075,28 +4075,28 @@
         <v>15.8</v>
       </c>
       <c r="M34">
-        <v>1.672624</v>
+        <v>1.7248935</v>
       </c>
       <c r="N34">
-        <v>14.127376</v>
+        <v>14.0751065</v>
       </c>
       <c r="O34">
-        <v>3.108022720000001</v>
+        <v>3.09652343</v>
       </c>
       <c r="P34">
-        <v>11.01935328</v>
+        <v>10.97858307</v>
       </c>
       <c r="Q34">
-        <v>21.71935328</v>
+        <v>21.67858307</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08899317082415513</v>
+        <v>0.08953409796410364</v>
       </c>
       <c r="T34">
-        <v>0.7282989123378181</v>
+        <v>0.7374197210249679</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.44623537627106</v>
+        <v>9.159985819414359</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07375874563594943</v>
+        <v>0.07364853511147337</v>
       </c>
       <c r="C35">
-        <v>68.90494068452848</v>
+        <v>68.05820365253035</v>
       </c>
       <c r="D35">
-        <v>70.24594068452849</v>
+        <v>70.37620365253034</v>
       </c>
       <c r="E35">
-        <v>14.341</v>
+        <v>15.318</v>
       </c>
       <c r="F35">
-        <v>32.241</v>
+        <v>33.218</v>
       </c>
       <c r="G35">
         <v>30.9</v>
@@ -4157,28 +4157,28 @@
         <v>15.8</v>
       </c>
       <c r="M35">
-        <v>1.7248935</v>
+        <v>1.777163</v>
       </c>
       <c r="N35">
-        <v>14.0751065</v>
+        <v>14.022837</v>
       </c>
       <c r="O35">
-        <v>3.09652343</v>
+        <v>3.08502414</v>
       </c>
       <c r="P35">
-        <v>10.97858307</v>
+        <v>10.93781286</v>
       </c>
       <c r="Q35">
-        <v>21.67858307</v>
+        <v>21.63781286</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08953409796410364</v>
+        <v>0.09009141683556574</v>
       </c>
       <c r="T35">
-        <v>0.7374197210249679</v>
+        <v>0.7468169178541527</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.159985819414359</v>
+        <v>8.890574471784525</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07364853511147337</v>
+        <v>0.07353832458699733</v>
       </c>
       <c r="C36">
-        <v>68.05820365253035</v>
+        <v>67.21195063327755</v>
       </c>
       <c r="D36">
-        <v>70.37620365253034</v>
+        <v>70.50695063327754</v>
       </c>
       <c r="E36">
-        <v>15.318</v>
+        <v>16.295</v>
       </c>
       <c r="F36">
-        <v>33.218</v>
+        <v>34.195</v>
       </c>
       <c r="G36">
         <v>30.9</v>
@@ -4239,28 +4239,28 @@
         <v>15.8</v>
       </c>
       <c r="M36">
-        <v>1.777163</v>
+        <v>1.8294325</v>
       </c>
       <c r="N36">
-        <v>14.022837</v>
+        <v>13.9705675</v>
       </c>
       <c r="O36">
-        <v>3.08502414</v>
+        <v>3.073524850000001</v>
       </c>
       <c r="P36">
-        <v>10.93781286</v>
+        <v>10.89704265</v>
       </c>
       <c r="Q36">
-        <v>21.63781286</v>
+        <v>21.59704265</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09009141683556574</v>
+        <v>0.09066588397999589</v>
       </c>
       <c r="T36">
-        <v>0.7468169178541527</v>
+        <v>0.7565032592011587</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.890574471784525</v>
+        <v>8.636558058304967</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07353832458699733</v>
+        <v>0.07342811406252128</v>
       </c>
       <c r="C37">
-        <v>67.21195063327755</v>
+        <v>66.36618432943052</v>
       </c>
       <c r="D37">
-        <v>70.50695063327754</v>
+        <v>70.63818432943053</v>
       </c>
       <c r="E37">
-        <v>16.295</v>
+        <v>17.272</v>
       </c>
       <c r="F37">
-        <v>34.195</v>
+        <v>35.172</v>
       </c>
       <c r="G37">
         <v>30.9</v>
@@ -4321,28 +4321,28 @@
         <v>15.8</v>
       </c>
       <c r="M37">
-        <v>1.8294325</v>
+        <v>1.881702</v>
       </c>
       <c r="N37">
-        <v>13.9705675</v>
+        <v>13.918298</v>
       </c>
       <c r="O37">
-        <v>3.073524850000001</v>
+        <v>3.06202556</v>
       </c>
       <c r="P37">
-        <v>10.89704265</v>
+        <v>10.85627244</v>
       </c>
       <c r="Q37">
-        <v>21.59704265</v>
+        <v>21.55627244</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09066588397999589</v>
+        <v>0.09125830322268952</v>
       </c>
       <c r="T37">
-        <v>0.7565032592011587</v>
+        <v>0.7664922987152585</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.636558058304967</v>
+        <v>8.396653667796496</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07342811406252128</v>
+        <v>0.07331790353804524</v>
       </c>
       <c r="C38">
-        <v>66.36618432943052</v>
+        <v>65.52090746380895</v>
       </c>
       <c r="D38">
-        <v>70.63818432943053</v>
+        <v>70.76990746380896</v>
       </c>
       <c r="E38">
-        <v>17.272</v>
+        <v>18.249</v>
       </c>
       <c r="F38">
-        <v>35.172</v>
+        <v>36.14899999999999</v>
       </c>
       <c r="G38">
         <v>30.9</v>
@@ -4403,28 +4403,28 @@
         <v>15.8</v>
       </c>
       <c r="M38">
-        <v>1.881702</v>
+        <v>1.9339715</v>
       </c>
       <c r="N38">
-        <v>13.918298</v>
+        <v>13.8660285</v>
       </c>
       <c r="O38">
-        <v>3.06202556</v>
+        <v>3.05052627</v>
       </c>
       <c r="P38">
-        <v>10.85627244</v>
+        <v>10.81550223</v>
       </c>
       <c r="Q38">
-        <v>21.55627244</v>
+        <v>21.51550223</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0912583032226895</v>
+        <v>0.09186952942546862</v>
       </c>
       <c r="T38">
-        <v>0.7664922987152584</v>
+        <v>0.7767984505948852</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.396653667796496</v>
+        <v>8.169717082180375</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07331790353804524</v>
+        <v>0.07320769301356919</v>
       </c>
       <c r="C39">
-        <v>65.52090746380895</v>
+        <v>64.67612277958003</v>
       </c>
       <c r="D39">
-        <v>70.76990746380896</v>
+        <v>70.90212277958004</v>
       </c>
       <c r="E39">
-        <v>18.249</v>
+        <v>19.226</v>
       </c>
       <c r="F39">
-        <v>36.14899999999999</v>
+        <v>37.126</v>
       </c>
       <c r="G39">
         <v>30.9</v>
@@ -4485,28 +4485,28 @@
         <v>15.8</v>
       </c>
       <c r="M39">
-        <v>1.9339715</v>
+        <v>1.986241</v>
       </c>
       <c r="N39">
-        <v>13.8660285</v>
+        <v>13.813759</v>
       </c>
       <c r="O39">
-        <v>3.05052627</v>
+        <v>3.03902698</v>
       </c>
       <c r="P39">
-        <v>10.81550223</v>
+        <v>10.77473202</v>
       </c>
       <c r="Q39">
-        <v>21.51550223</v>
+        <v>21.47473202</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09186952942546862</v>
+        <v>0.09250047260253094</v>
       </c>
       <c r="T39">
-        <v>0.7767984505948852</v>
+        <v>0.787437058986758</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.169717082180375</v>
+        <v>7.954724527386154</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07320769301356919</v>
+        <v>0.07309748248909313</v>
       </c>
       <c r="C40">
-        <v>64.67612277958003</v>
+        <v>63.83183304044893</v>
       </c>
       <c r="D40">
-        <v>70.90212277958004</v>
+        <v>71.03483304044893</v>
       </c>
       <c r="E40">
-        <v>19.226</v>
+        <v>20.203</v>
       </c>
       <c r="F40">
-        <v>37.126</v>
+        <v>38.10299999999999</v>
       </c>
       <c r="G40">
         <v>30.9</v>
@@ -4567,28 +4567,28 @@
         <v>15.8</v>
       </c>
       <c r="M40">
-        <v>1.986241</v>
+        <v>2.0385105</v>
       </c>
       <c r="N40">
-        <v>13.813759</v>
+        <v>13.7614895</v>
       </c>
       <c r="O40">
-        <v>3.03902698</v>
+        <v>3.02752769</v>
       </c>
       <c r="P40">
-        <v>10.77473202</v>
+        <v>10.73396181</v>
       </c>
       <c r="Q40">
-        <v>21.47473202</v>
+        <v>21.43396181</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09250047260253094</v>
+        <v>0.09315210244113628</v>
       </c>
       <c r="T40">
-        <v>0.787437058986758</v>
+        <v>0.7984244742111513</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.954724527386154</v>
+        <v>7.750757231812151</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07309748248909313</v>
+        <v>0.07323687196461709</v>
       </c>
       <c r="C41">
-        <v>63.83183304044893</v>
+        <v>62.68706985798353</v>
       </c>
       <c r="D41">
-        <v>71.03483304044893</v>
+        <v>70.86706985798352</v>
       </c>
       <c r="E41">
-        <v>20.203</v>
+        <v>21.18</v>
       </c>
       <c r="F41">
-        <v>38.10299999999999</v>
+        <v>39.08</v>
       </c>
       <c r="G41">
         <v>30.9</v>
@@ -4649,45 +4649,45 @@
         <v>15.8</v>
       </c>
       <c r="M41">
-        <v>2.0385105</v>
+        <v>2.122044</v>
       </c>
       <c r="N41">
-        <v>13.7614895</v>
+        <v>13.677956</v>
       </c>
       <c r="O41">
-        <v>3.02752769</v>
+        <v>3.00915032</v>
       </c>
       <c r="P41">
-        <v>10.73396181</v>
+        <v>10.66880568</v>
       </c>
       <c r="Q41">
-        <v>21.43396181</v>
+        <v>21.36880568</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09315210244113628</v>
+        <v>0.09382545327436181</v>
       </c>
       <c r="T41">
-        <v>0.7984244742111513</v>
+        <v>0.8097781366096909</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.750757231812151</v>
+        <v>7.44565145680297</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07323687196461709</v>
+        <v>0.07313290144014103</v>
       </c>
       <c r="C42">
-        <v>62.68706985798353</v>
+        <v>61.83512908611899</v>
       </c>
       <c r="D42">
-        <v>70.86706985798352</v>
+        <v>70.99212908611898</v>
       </c>
       <c r="E42">
-        <v>21.18</v>
+        <v>22.157</v>
       </c>
       <c r="F42">
-        <v>39.08</v>
+        <v>40.057</v>
       </c>
       <c r="G42">
         <v>30.9</v>
@@ -4731,28 +4731,28 @@
         <v>15.8</v>
       </c>
       <c r="M42">
-        <v>2.122044</v>
+        <v>2.1750951</v>
       </c>
       <c r="N42">
-        <v>13.677956</v>
+        <v>13.6249049</v>
       </c>
       <c r="O42">
-        <v>3.00915032</v>
+        <v>2.997479078</v>
       </c>
       <c r="P42">
-        <v>10.66880568</v>
+        <v>10.627425822</v>
       </c>
       <c r="Q42">
-        <v>21.36880568</v>
+        <v>21.327425822</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09382545327436181</v>
+        <v>0.09452162955956107</v>
       </c>
       <c r="T42">
-        <v>0.8097781366096909</v>
+        <v>0.8215166689200455</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.44565145680297</v>
+        <v>7.264050201758995</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07313290144014103</v>
+        <v>0.07302893091566498</v>
       </c>
       <c r="C43">
-        <v>61.83512908611899</v>
+        <v>60.98363047897106</v>
       </c>
       <c r="D43">
-        <v>70.99212908611898</v>
+        <v>71.11763047897107</v>
       </c>
       <c r="E43">
-        <v>22.157</v>
+        <v>23.134</v>
       </c>
       <c r="F43">
-        <v>40.057</v>
+        <v>41.034</v>
       </c>
       <c r="G43">
         <v>30.9</v>
@@ -4813,28 +4813,28 @@
         <v>15.8</v>
       </c>
       <c r="M43">
-        <v>2.1750951</v>
+        <v>2.2281462</v>
       </c>
       <c r="N43">
-        <v>13.6249049</v>
+        <v>13.5718538</v>
       </c>
       <c r="O43">
-        <v>2.997479078</v>
+        <v>2.985807836</v>
       </c>
       <c r="P43">
-        <v>10.627425822</v>
+        <v>10.586045964</v>
       </c>
       <c r="Q43">
-        <v>21.327425822</v>
+        <v>21.286045964</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09452162955956107</v>
+        <v>0.09524181192356032</v>
       </c>
       <c r="T43">
-        <v>0.8215166689200455</v>
+        <v>0.8336599782066192</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.264050201758995</v>
+        <v>7.091096625526638</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07302893091566499</v>
+        <v>0.07292496039118894</v>
       </c>
       <c r="C44">
-        <v>60.98363047897104</v>
+        <v>60.13257638569715</v>
       </c>
       <c r="D44">
-        <v>71.11763047897104</v>
+        <v>71.24357638569715</v>
       </c>
       <c r="E44">
-        <v>23.13399999999999</v>
+        <v>24.111</v>
       </c>
       <c r="F44">
-        <v>41.03399999999999</v>
+        <v>42.011</v>
       </c>
       <c r="G44">
         <v>30.9</v>
@@ -4895,28 +4895,28 @@
         <v>15.8</v>
       </c>
       <c r="M44">
-        <v>2.228146199999999</v>
+        <v>2.2811973</v>
       </c>
       <c r="N44">
-        <v>13.5718538</v>
+        <v>13.5188027</v>
       </c>
       <c r="O44">
-        <v>2.985807836</v>
+        <v>2.974136594</v>
       </c>
       <c r="P44">
-        <v>10.586045964</v>
+        <v>10.544666106</v>
       </c>
       <c r="Q44">
-        <v>21.286045964</v>
+        <v>21.244666106</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09524181192356032</v>
+        <v>0.09598726384419111</v>
       </c>
       <c r="T44">
-        <v>0.8336599782066192</v>
+        <v>0.8462293685207919</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.09109662552664</v>
+        <v>6.926187401677183</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07292496039118894</v>
+        <v>0.0728209898667129</v>
       </c>
       <c r="C45">
-        <v>60.13257638569715</v>
+        <v>59.28196917212521</v>
       </c>
       <c r="D45">
-        <v>71.24357638569715</v>
+        <v>71.3699691721252</v>
       </c>
       <c r="E45">
-        <v>24.111</v>
+        <v>25.08799999999999</v>
       </c>
       <c r="F45">
-        <v>42.011</v>
+        <v>42.98799999999999</v>
       </c>
       <c r="G45">
         <v>30.9</v>
@@ -4977,28 +4977,28 @@
         <v>15.8</v>
       </c>
       <c r="M45">
-        <v>2.2811973</v>
+        <v>2.334248399999999</v>
       </c>
       <c r="N45">
-        <v>13.5188027</v>
+        <v>13.4657516</v>
       </c>
       <c r="O45">
-        <v>2.974136594</v>
+        <v>2.962465352</v>
       </c>
       <c r="P45">
-        <v>10.544666106</v>
+        <v>10.503286248</v>
       </c>
       <c r="Q45">
-        <v>21.244666106</v>
+        <v>21.203286248</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09598726384419111</v>
+        <v>0.09675933904770158</v>
       </c>
       <c r="T45">
-        <v>0.8462293685207919</v>
+        <v>0.8592476656318995</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.926187401677183</v>
+        <v>6.768774051639064</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0728209898667129</v>
+        <v>0.07271701934223684</v>
       </c>
       <c r="C46">
-        <v>59.28196917212521</v>
+        <v>58.43181122090176</v>
       </c>
       <c r="D46">
-        <v>71.3699691721252</v>
+        <v>71.49681122090175</v>
       </c>
       <c r="E46">
-        <v>25.08799999999999</v>
+        <v>26.065</v>
       </c>
       <c r="F46">
-        <v>42.98799999999999</v>
+        <v>43.965</v>
       </c>
       <c r="G46">
         <v>30.9</v>
@@ -5059,28 +5059,28 @@
         <v>15.8</v>
       </c>
       <c r="M46">
-        <v>2.334248399999999</v>
+        <v>2.3872995</v>
       </c>
       <c r="N46">
-        <v>13.4657516</v>
+        <v>13.4127005</v>
       </c>
       <c r="O46">
-        <v>2.962465352</v>
+        <v>2.95079411</v>
       </c>
       <c r="P46">
-        <v>10.503286248</v>
+        <v>10.46190639</v>
       </c>
       <c r="Q46">
-        <v>21.203286248</v>
+        <v>21.16190639</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09675933904770158</v>
+        <v>0.09755948971315788</v>
       </c>
       <c r="T46">
-        <v>0.8592476656318995</v>
+        <v>0.8727393553652291</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.768774051639064</v>
+        <v>6.618356850491529</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07271701934223684</v>
+        <v>0.07261304881776079</v>
       </c>
       <c r="C47">
-        <v>58.43181122090176</v>
+        <v>57.58210493164172</v>
       </c>
       <c r="D47">
-        <v>71.49681122090175</v>
+        <v>71.62410493164171</v>
       </c>
       <c r="E47">
-        <v>26.065</v>
+        <v>27.042</v>
       </c>
       <c r="F47">
-        <v>43.965</v>
+        <v>44.942</v>
       </c>
       <c r="G47">
         <v>30.9</v>
@@ -5141,28 +5141,28 @@
         <v>15.8</v>
       </c>
       <c r="M47">
-        <v>2.3872995</v>
+        <v>2.4403506</v>
       </c>
       <c r="N47">
-        <v>13.4127005</v>
+        <v>13.3596494</v>
       </c>
       <c r="O47">
-        <v>2.95079411</v>
+        <v>2.939122868</v>
       </c>
       <c r="P47">
-        <v>10.46190639</v>
+        <v>10.420526532</v>
       </c>
       <c r="Q47">
-        <v>21.16190639</v>
+        <v>21.120526532</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09755948971315788</v>
+        <v>0.09838927558844589</v>
       </c>
       <c r="T47">
-        <v>0.8727393553652291</v>
+        <v>0.8867307373109041</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.618356850491529</v>
+        <v>6.474479527654756</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07261304881776079</v>
+        <v>0.07250907829328473</v>
       </c>
       <c r="C48">
-        <v>57.58210493164172</v>
+        <v>56.73285272107965</v>
       </c>
       <c r="D48">
-        <v>71.62410493164171</v>
+        <v>71.75185272107966</v>
       </c>
       <c r="E48">
-        <v>27.042</v>
+        <v>28.019</v>
       </c>
       <c r="F48">
-        <v>44.942</v>
+        <v>45.919</v>
       </c>
       <c r="G48">
         <v>30.9</v>
@@ -5223,28 +5223,28 @@
         <v>15.8</v>
       </c>
       <c r="M48">
-        <v>2.4403506</v>
+        <v>2.4934017</v>
       </c>
       <c r="N48">
-        <v>13.3596494</v>
+        <v>13.3065983</v>
       </c>
       <c r="O48">
-        <v>2.939122868</v>
+        <v>2.927451626</v>
       </c>
       <c r="P48">
-        <v>10.420526532</v>
+        <v>10.379146674</v>
       </c>
       <c r="Q48">
-        <v>21.120526532</v>
+        <v>21.079146674</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09838927558844589</v>
+        <v>0.09925037413827309</v>
       </c>
       <c r="T48">
-        <v>0.8867307373109041</v>
+        <v>0.9012500959337747</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.474479527654756</v>
+        <v>6.336724644087634</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07250907829328473</v>
+        <v>0.07240510776880869</v>
       </c>
       <c r="C49">
-        <v>56.73285272107965</v>
+        <v>55.88405702322281</v>
       </c>
       <c r="D49">
-        <v>71.75185272107966</v>
+        <v>71.88005702322282</v>
       </c>
       <c r="E49">
-        <v>28.019</v>
+        <v>28.996</v>
       </c>
       <c r="F49">
-        <v>45.919</v>
+        <v>46.896</v>
       </c>
       <c r="G49">
         <v>30.9</v>
@@ -5305,28 +5305,28 @@
         <v>15.8</v>
       </c>
       <c r="M49">
-        <v>2.4934017</v>
+        <v>2.5464528</v>
       </c>
       <c r="N49">
-        <v>13.3065983</v>
+        <v>13.2535472</v>
       </c>
       <c r="O49">
-        <v>2.927451626</v>
+        <v>2.915780384</v>
       </c>
       <c r="P49">
-        <v>10.379146674</v>
+        <v>10.337766816</v>
       </c>
       <c r="Q49">
-        <v>21.079146674</v>
+        <v>21.037766816</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09925037413827309</v>
+        <v>0.1001445918630936</v>
       </c>
       <c r="T49">
-        <v>0.9012500959337747</v>
+        <v>0.9163278914267555</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.336724644087634</v>
+        <v>6.204709547335808</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07240510776880868</v>
+        <v>0.07268333724433264</v>
       </c>
       <c r="C50">
-        <v>55.88405702322284</v>
+        <v>54.56499947936589</v>
       </c>
       <c r="D50">
-        <v>71.88005702322283</v>
+        <v>71.53799947936589</v>
       </c>
       <c r="E50">
-        <v>28.996</v>
+        <v>29.97299999999999</v>
       </c>
       <c r="F50">
-        <v>46.89599999999999</v>
+        <v>47.87299999999999</v>
       </c>
       <c r="G50">
         <v>30.9</v>
@@ -5387,45 +5387,45 @@
         <v>15.8</v>
       </c>
       <c r="M50">
-        <v>2.5464528</v>
+        <v>2.647376899999999</v>
       </c>
       <c r="N50">
-        <v>13.2535472</v>
+        <v>13.1526231</v>
       </c>
       <c r="O50">
-        <v>2.915780384000001</v>
+        <v>2.893577082</v>
       </c>
       <c r="P50">
-        <v>10.337766816</v>
+        <v>10.259046018</v>
       </c>
       <c r="Q50">
-        <v>21.037766816</v>
+        <v>20.959046018</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1001445918630936</v>
+        <v>0.1010738769496718</v>
       </c>
       <c r="T50">
-        <v>0.9163278914267554</v>
+        <v>0.9319969730175003</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.204709547335809</v>
+        <v>5.968171740109995</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07268333724433264</v>
+        <v>0.07258716671985659</v>
       </c>
       <c r="C51">
-        <v>54.56499947936589</v>
+        <v>53.70586352431584</v>
       </c>
       <c r="D51">
-        <v>71.53799947936589</v>
+        <v>71.65586352431583</v>
       </c>
       <c r="E51">
-        <v>29.97299999999999</v>
+        <v>30.95</v>
       </c>
       <c r="F51">
-        <v>47.87299999999999</v>
+        <v>48.84999999999999</v>
       </c>
       <c r="G51">
         <v>30.9</v>
@@ -5469,28 +5469,28 @@
         <v>15.8</v>
       </c>
       <c r="M51">
-        <v>2.647376899999999</v>
+        <v>2.701405</v>
       </c>
       <c r="N51">
-        <v>13.1526231</v>
+        <v>13.098595</v>
       </c>
       <c r="O51">
-        <v>2.893577082</v>
+        <v>2.8816909</v>
       </c>
       <c r="P51">
-        <v>10.259046018</v>
+        <v>10.2169041</v>
       </c>
       <c r="Q51">
-        <v>20.959046018</v>
+        <v>20.9169041</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1010738769496718</v>
+        <v>0.1020403334397132</v>
       </c>
       <c r="T51">
-        <v>0.9319969730175003</v>
+        <v>0.9482928178718749</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.968171740109995</v>
+        <v>5.848808305307794</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07258716671985659</v>
+        <v>0.07249099619538053</v>
       </c>
       <c r="C52">
-        <v>53.70586352431584</v>
+        <v>52.84711658933716</v>
       </c>
       <c r="D52">
-        <v>71.65586352431583</v>
+        <v>71.77411658933715</v>
       </c>
       <c r="E52">
-        <v>30.95</v>
+        <v>31.927</v>
       </c>
       <c r="F52">
-        <v>48.84999999999999</v>
+        <v>49.827</v>
       </c>
       <c r="G52">
         <v>30.9</v>
@@ -5551,28 +5551,28 @@
         <v>15.8</v>
       </c>
       <c r="M52">
-        <v>2.701405</v>
+        <v>2.7554331</v>
       </c>
       <c r="N52">
-        <v>13.098595</v>
+        <v>13.0445669</v>
       </c>
       <c r="O52">
-        <v>2.8816909</v>
+        <v>2.869804718</v>
       </c>
       <c r="P52">
-        <v>10.2169041</v>
+        <v>10.174762182</v>
       </c>
       <c r="Q52">
-        <v>20.9169041</v>
+        <v>20.874762182</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1020403334397132</v>
+        <v>0.1030462371334297</v>
       </c>
       <c r="T52">
-        <v>0.9482928178718749</v>
+        <v>0.9652537992509179</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.848808305307794</v>
+        <v>5.734125789517446</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07249099619538053</v>
+        <v>0.07239482567090448</v>
       </c>
       <c r="C53">
-        <v>52.84711658933716</v>
+        <v>51.98876060360312</v>
       </c>
       <c r="D53">
-        <v>71.77411658933715</v>
+        <v>71.89276060360312</v>
       </c>
       <c r="E53">
-        <v>31.927</v>
+        <v>32.904</v>
       </c>
       <c r="F53">
-        <v>49.827</v>
+        <v>50.80399999999999</v>
       </c>
       <c r="G53">
         <v>30.9</v>
@@ -5633,28 +5633,28 @@
         <v>15.8</v>
       </c>
       <c r="M53">
-        <v>2.7554331</v>
+        <v>2.8094612</v>
       </c>
       <c r="N53">
-        <v>13.0445669</v>
+        <v>12.9905388</v>
       </c>
       <c r="O53">
-        <v>2.869804718</v>
+        <v>2.857918536</v>
       </c>
       <c r="P53">
-        <v>10.174762182</v>
+        <v>10.132620264</v>
       </c>
       <c r="Q53">
-        <v>20.874762182</v>
+        <v>20.832620264</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1030462371334297</v>
+        <v>0.104094053481051</v>
       </c>
       <c r="T53">
-        <v>0.9652537992509179</v>
+        <v>0.982921488187421</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.734125789517446</v>
+        <v>5.623854139719032</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07239482567090448</v>
+        <v>0.07229865514642844</v>
       </c>
       <c r="C54">
-        <v>51.98876060360312</v>
+        <v>51.130797509064</v>
       </c>
       <c r="D54">
-        <v>71.89276060360312</v>
+        <v>72.01179750906401</v>
       </c>
       <c r="E54">
-        <v>32.904</v>
+        <v>33.881</v>
       </c>
       <c r="F54">
-        <v>50.80399999999999</v>
+        <v>51.781</v>
       </c>
       <c r="G54">
         <v>30.9</v>
@@ -5715,28 +5715,28 @@
         <v>15.8</v>
       </c>
       <c r="M54">
-        <v>2.8094612</v>
+        <v>2.8634893</v>
       </c>
       <c r="N54">
-        <v>12.9905388</v>
+        <v>12.9365107</v>
       </c>
       <c r="O54">
-        <v>2.857918536</v>
+        <v>2.846032354</v>
       </c>
       <c r="P54">
-        <v>10.132620264</v>
+        <v>10.090478346</v>
       </c>
       <c r="Q54">
-        <v>20.832620264</v>
+        <v>20.790478346</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.104094053481051</v>
+        <v>0.1051864577583584</v>
       </c>
       <c r="T54">
-        <v>0.982921488187421</v>
+        <v>1.001340993674414</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.623854139719032</v>
+        <v>5.517743684252636</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07229865514642844</v>
+        <v>0.07220248462195239</v>
       </c>
       <c r="C55">
-        <v>51.130797509064</v>
+        <v>50.27322926055298</v>
       </c>
       <c r="D55">
-        <v>72.01179750906401</v>
+        <v>72.13122926055298</v>
       </c>
       <c r="E55">
-        <v>33.881</v>
+        <v>34.858</v>
       </c>
       <c r="F55">
-        <v>51.781</v>
+        <v>52.758</v>
       </c>
       <c r="G55">
         <v>30.9</v>
@@ -5797,28 +5797,28 @@
         <v>15.8</v>
       </c>
       <c r="M55">
-        <v>2.8634893</v>
+        <v>2.9175174</v>
       </c>
       <c r="N55">
-        <v>12.9365107</v>
+        <v>12.8824826</v>
       </c>
       <c r="O55">
-        <v>2.846032354</v>
+        <v>2.834146172</v>
       </c>
       <c r="P55">
-        <v>10.090478346</v>
+        <v>10.048336428</v>
       </c>
       <c r="Q55">
-        <v>20.790478346</v>
+        <v>20.748336428</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1051864577583584</v>
+        <v>0.1063263578738095</v>
       </c>
       <c r="T55">
-        <v>1.001340993674414</v>
+        <v>1.020561347226058</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.517743684252636</v>
+        <v>5.415563245655365</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07220248462195239</v>
+        <v>0.07210631409747634</v>
       </c>
       <c r="C56">
-        <v>50.27322926055298</v>
+        <v>49.41605782589316</v>
       </c>
       <c r="D56">
-        <v>72.13122926055298</v>
+        <v>72.25105782589316</v>
       </c>
       <c r="E56">
-        <v>34.858</v>
+        <v>35.835</v>
       </c>
       <c r="F56">
-        <v>52.758</v>
+        <v>53.735</v>
       </c>
       <c r="G56">
         <v>30.9</v>
@@ -5879,28 +5879,28 @@
         <v>15.8</v>
       </c>
       <c r="M56">
-        <v>2.9175174</v>
+        <v>2.9715455</v>
       </c>
       <c r="N56">
-        <v>12.8824826</v>
+        <v>12.8284545</v>
       </c>
       <c r="O56">
-        <v>2.834146172</v>
+        <v>2.82225999</v>
       </c>
       <c r="P56">
-        <v>10.048336428</v>
+        <v>10.00619451</v>
       </c>
       <c r="Q56">
-        <v>20.748336428</v>
+        <v>20.70619451</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1063263578738095</v>
+        <v>0.1075169202166141</v>
       </c>
       <c r="T56">
-        <v>1.020561347226058</v>
+        <v>1.040635938713331</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.415563245655365</v>
+        <v>5.317098459370722</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07210631409747634</v>
+        <v>0.07201014357300028</v>
       </c>
       <c r="C57">
-        <v>49.41605782589316</v>
+        <v>48.55928518600563</v>
       </c>
       <c r="D57">
-        <v>72.25105782589316</v>
+        <v>72.37128518600562</v>
       </c>
       <c r="E57">
-        <v>35.835</v>
+        <v>36.812</v>
       </c>
       <c r="F57">
-        <v>53.735</v>
+        <v>54.712</v>
       </c>
       <c r="G57">
         <v>30.9</v>
@@ -5961,28 +5961,28 @@
         <v>15.8</v>
       </c>
       <c r="M57">
-        <v>2.9715455</v>
+        <v>3.0255736</v>
       </c>
       <c r="N57">
-        <v>12.8284545</v>
+        <v>12.7744264</v>
       </c>
       <c r="O57">
-        <v>2.82225999</v>
+        <v>2.810373808</v>
       </c>
       <c r="P57">
-        <v>10.00619451</v>
+        <v>9.964052592000002</v>
       </c>
       <c r="Q57">
-        <v>20.70619451</v>
+        <v>20.664052592</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1075169202166141</v>
+        <v>0.1087615990295461</v>
       </c>
       <c r="T57">
-        <v>1.040635938713331</v>
+        <v>1.061623011631844</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.317098459370722</v>
+        <v>5.222150272596244</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07201014357300028</v>
+        <v>0.07191397304852423</v>
       </c>
       <c r="C58">
-        <v>48.55928518600563</v>
+        <v>47.70291333501867</v>
       </c>
       <c r="D58">
-        <v>72.37128518600562</v>
+        <v>72.49191333501867</v>
       </c>
       <c r="E58">
-        <v>36.812</v>
+        <v>37.789</v>
       </c>
       <c r="F58">
-        <v>54.712</v>
+        <v>55.689</v>
       </c>
       <c r="G58">
         <v>30.9</v>
@@ -6043,28 +6043,28 @@
         <v>15.8</v>
       </c>
       <c r="M58">
-        <v>3.0255736</v>
+        <v>3.0796017</v>
       </c>
       <c r="N58">
-        <v>12.7744264</v>
+        <v>12.7203983</v>
       </c>
       <c r="O58">
-        <v>2.810373808</v>
+        <v>2.798487626</v>
       </c>
       <c r="P58">
-        <v>9.964052592000002</v>
+        <v>9.921910674000001</v>
       </c>
       <c r="Q58">
-        <v>20.664052592</v>
+        <v>20.621910674</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1087615990295461</v>
+        <v>0.1100641698802889</v>
       </c>
       <c r="T58">
-        <v>1.061623011631844</v>
+        <v>1.083586227476799</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.222150272596244</v>
+        <v>5.130533601147188</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07191397304852423</v>
+        <v>0.07181780252404819</v>
       </c>
       <c r="C59">
-        <v>47.70291333501867</v>
+        <v>46.84694428037793</v>
       </c>
       <c r="D59">
-        <v>72.49191333501867</v>
+        <v>72.61294428037793</v>
       </c>
       <c r="E59">
-        <v>37.789</v>
+        <v>38.766</v>
       </c>
       <c r="F59">
-        <v>55.689</v>
+        <v>56.666</v>
       </c>
       <c r="G59">
         <v>30.9</v>
@@ -6125,28 +6125,28 @@
         <v>15.8</v>
       </c>
       <c r="M59">
-        <v>3.0796017</v>
+        <v>3.1336298</v>
       </c>
       <c r="N59">
-        <v>12.7203983</v>
+        <v>12.6663702</v>
       </c>
       <c r="O59">
-        <v>2.798487626</v>
+        <v>2.786601444</v>
       </c>
       <c r="P59">
-        <v>9.921910674000001</v>
+        <v>9.879768756000001</v>
       </c>
       <c r="Q59">
-        <v>20.621910674</v>
+        <v>20.579768756</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1100641698802889</v>
+        <v>0.1114287679144005</v>
       </c>
       <c r="T59">
-        <v>1.083586227476799</v>
+        <v>1.106595310742942</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.130533601147188</v>
+        <v>5.042076125265339</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07181780252404818</v>
+        <v>0.07172163199957213</v>
       </c>
       <c r="C60">
-        <v>46.84694428037796</v>
+        <v>45.99138004295794</v>
       </c>
       <c r="D60">
-        <v>72.61294428037795</v>
+        <v>72.73438004295794</v>
       </c>
       <c r="E60">
-        <v>38.76599999999999</v>
+        <v>39.74299999999999</v>
       </c>
       <c r="F60">
-        <v>56.66599999999999</v>
+        <v>57.64299999999999</v>
       </c>
       <c r="G60">
         <v>30.9</v>
@@ -6207,28 +6207,28 @@
         <v>15.8</v>
       </c>
       <c r="M60">
-        <v>3.1336298</v>
+        <v>3.1876579</v>
       </c>
       <c r="N60">
-        <v>12.6663702</v>
+        <v>12.6123421</v>
       </c>
       <c r="O60">
-        <v>2.786601444</v>
+        <v>2.774715262</v>
       </c>
       <c r="P60">
-        <v>9.879768756000001</v>
+        <v>9.837626838</v>
       </c>
       <c r="Q60">
-        <v>20.579768756</v>
+        <v>20.537626838</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1114287679144004</v>
+        <v>0.1128599317062735</v>
       </c>
       <c r="T60">
-        <v>1.106595310742942</v>
+        <v>1.130726788314751</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.04207612526534</v>
+        <v>4.956617207887962</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07172163199957213</v>
+        <v>0.07162546147509609</v>
       </c>
       <c r="C61">
-        <v>45.99138004295794</v>
+        <v>45.13622265717434</v>
       </c>
       <c r="D61">
-        <v>72.73438004295794</v>
+        <v>72.85622265717433</v>
       </c>
       <c r="E61">
-        <v>39.74299999999999</v>
+        <v>40.71999999999999</v>
       </c>
       <c r="F61">
-        <v>57.64299999999999</v>
+        <v>58.61999999999999</v>
       </c>
       <c r="G61">
         <v>30.9</v>
@@ -6289,28 +6289,28 @@
         <v>15.8</v>
       </c>
       <c r="M61">
-        <v>3.1876579</v>
+        <v>3.241686</v>
       </c>
       <c r="N61">
-        <v>12.6123421</v>
+        <v>12.558314</v>
       </c>
       <c r="O61">
-        <v>2.774715262</v>
+        <v>2.76282908</v>
       </c>
       <c r="P61">
-        <v>9.837626838</v>
+        <v>9.79548492</v>
       </c>
       <c r="Q61">
-        <v>20.537626838</v>
+        <v>20.49548492</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1128599317062735</v>
+        <v>0.1143626536877402</v>
       </c>
       <c r="T61">
-        <v>1.130726788314751</v>
+        <v>1.156064839765151</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.956617207887962</v>
+        <v>4.874006921089829</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07162546147509609</v>
+        <v>0.07152929095062004</v>
       </c>
       <c r="C62">
-        <v>45.13622265717434</v>
+        <v>44.28147417109774</v>
       </c>
       <c r="D62">
-        <v>72.85622265717433</v>
+        <v>72.97847417109773</v>
       </c>
       <c r="E62">
-        <v>40.71999999999999</v>
+        <v>41.697</v>
       </c>
       <c r="F62">
-        <v>58.61999999999999</v>
+        <v>59.59699999999999</v>
       </c>
       <c r="G62">
         <v>30.9</v>
@@ -6371,28 +6371,28 @@
         <v>15.8</v>
       </c>
       <c r="M62">
-        <v>3.241686</v>
+        <v>3.2957141</v>
       </c>
       <c r="N62">
-        <v>12.558314</v>
+        <v>12.5042859</v>
       </c>
       <c r="O62">
-        <v>2.76282908</v>
+        <v>2.750942898</v>
       </c>
       <c r="P62">
-        <v>9.79548492</v>
+        <v>9.753343002000001</v>
       </c>
       <c r="Q62">
-        <v>20.49548492</v>
+        <v>20.453343002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1143626536877402</v>
+        <v>0.1159424383349232</v>
       </c>
       <c r="T62">
-        <v>1.156064839765151</v>
+        <v>1.182702278469417</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.874006921089829</v>
+        <v>4.794105168285077</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07152929095062004</v>
+        <v>0.07143312042614398</v>
       </c>
       <c r="C63">
-        <v>44.28147417109774</v>
+        <v>43.42713664656829</v>
       </c>
       <c r="D63">
-        <v>72.97847417109773</v>
+        <v>73.10113664656829</v>
       </c>
       <c r="E63">
-        <v>41.697</v>
+        <v>42.67399999999999</v>
       </c>
       <c r="F63">
-        <v>59.59699999999999</v>
+        <v>60.57399999999999</v>
       </c>
       <c r="G63">
         <v>30.9</v>
@@ -6453,28 +6453,28 @@
         <v>15.8</v>
       </c>
       <c r="M63">
-        <v>3.2957141</v>
+        <v>3.3497422</v>
       </c>
       <c r="N63">
-        <v>12.5042859</v>
+        <v>12.4502578</v>
       </c>
       <c r="O63">
-        <v>2.750942898</v>
+        <v>2.739056716</v>
       </c>
       <c r="P63">
-        <v>9.753343002000001</v>
+        <v>9.711201084000001</v>
       </c>
       <c r="Q63">
-        <v>20.453343002</v>
+        <v>20.411201084</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1159424383349232</v>
+        <v>0.1176053695424842</v>
       </c>
       <c r="T63">
-        <v>1.182702278469417</v>
+        <v>1.210741687631802</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.794105168285077</v>
+        <v>4.716780891377253</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07143312042614398</v>
+        <v>0.07133694990166793</v>
       </c>
       <c r="C64">
-        <v>43.42713664656829</v>
+        <v>42.57321215931176</v>
       </c>
       <c r="D64">
-        <v>73.10113664656829</v>
+        <v>73.22421215931175</v>
       </c>
       <c r="E64">
-        <v>42.67399999999999</v>
+        <v>43.651</v>
       </c>
       <c r="F64">
-        <v>60.57399999999999</v>
+        <v>61.55099999999999</v>
       </c>
       <c r="G64">
         <v>30.9</v>
@@ -6535,28 +6535,28 @@
         <v>15.8</v>
       </c>
       <c r="M64">
-        <v>3.3497422</v>
+        <v>3.4037703</v>
       </c>
       <c r="N64">
-        <v>12.4502578</v>
+        <v>12.3962297</v>
       </c>
       <c r="O64">
-        <v>2.739056716</v>
+        <v>2.727170534</v>
       </c>
       <c r="P64">
-        <v>9.711201084000001</v>
+        <v>9.669059166</v>
       </c>
       <c r="Q64">
-        <v>20.411201084</v>
+        <v>20.369059166</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1176053695424842</v>
+        <v>0.1193581889234268</v>
       </c>
       <c r="T64">
-        <v>1.210741687631802</v>
+        <v>1.240296740532695</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.716780891377253</v>
+        <v>4.641911353418884</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07133694990166793</v>
+        <v>0.07124077937719188</v>
       </c>
       <c r="C65">
-        <v>42.57321215931176</v>
+        <v>41.71970279905645</v>
       </c>
       <c r="D65">
-        <v>73.22421215931175</v>
+        <v>73.34770279905645</v>
       </c>
       <c r="E65">
-        <v>43.651</v>
+        <v>44.62799999999999</v>
       </c>
       <c r="F65">
-        <v>61.55099999999999</v>
+        <v>62.52799999999999</v>
       </c>
       <c r="G65">
         <v>30.9</v>
@@ -6617,28 +6617,28 @@
         <v>15.8</v>
       </c>
       <c r="M65">
-        <v>3.4037703</v>
+        <v>3.4577984</v>
       </c>
       <c r="N65">
-        <v>12.3962297</v>
+        <v>12.3422016</v>
       </c>
       <c r="O65">
-        <v>2.727170534</v>
+        <v>2.715284352</v>
       </c>
       <c r="P65">
-        <v>9.669059166</v>
+        <v>9.626917248000002</v>
       </c>
       <c r="Q65">
-        <v>20.369059166</v>
+        <v>20.326917248</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1193581889234268</v>
+        <v>0.1212083871588663</v>
       </c>
       <c r="T65">
-        <v>1.240296740532695</v>
+        <v>1.271493740816971</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.641911353418884</v>
+        <v>4.569381488521714</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07124077937719188</v>
+        <v>0.07241210885271585</v>
       </c>
       <c r="C66">
-        <v>41.71970279905645</v>
+        <v>39.26640971994624</v>
       </c>
       <c r="D66">
-        <v>73.34770279905645</v>
+        <v>71.87140971994624</v>
       </c>
       <c r="E66">
-        <v>44.62799999999999</v>
+        <v>45.605</v>
       </c>
       <c r="F66">
-        <v>62.52799999999999</v>
+        <v>63.505</v>
       </c>
       <c r="G66">
         <v>30.9</v>
@@ -6699,45 +6699,45 @@
         <v>15.8</v>
       </c>
       <c r="M66">
-        <v>3.4577984</v>
+        <v>3.670589</v>
       </c>
       <c r="N66">
-        <v>12.3422016</v>
+        <v>12.129411</v>
       </c>
       <c r="O66">
-        <v>2.715284352</v>
+        <v>2.66847042</v>
       </c>
       <c r="P66">
-        <v>9.626917248000002</v>
+        <v>9.460940580000001</v>
       </c>
       <c r="Q66">
-        <v>20.326917248</v>
+        <v>20.16094058</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1212083871588663</v>
+        <v>0.1231643110077595</v>
       </c>
       <c r="T66">
-        <v>1.271493740816971</v>
+        <v>1.304473426831777</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.569381488521714</v>
+        <v>4.304486282719204</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07241210885271585</v>
+        <v>0.07233543832823978</v>
       </c>
       <c r="C67">
-        <v>39.26640971994624</v>
+        <v>38.38422190005139</v>
       </c>
       <c r="D67">
-        <v>71.87140971994624</v>
+        <v>71.96622190005139</v>
       </c>
       <c r="E67">
-        <v>45.605</v>
+        <v>46.582</v>
       </c>
       <c r="F67">
-        <v>63.505</v>
+        <v>64.482</v>
       </c>
       <c r="G67">
         <v>30.9</v>
@@ -6781,28 +6781,28 @@
         <v>15.8</v>
       </c>
       <c r="M67">
-        <v>3.670589</v>
+        <v>3.7270596</v>
       </c>
       <c r="N67">
-        <v>12.129411</v>
+        <v>12.0729404</v>
       </c>
       <c r="O67">
-        <v>2.66847042</v>
+        <v>2.656046888</v>
       </c>
       <c r="P67">
-        <v>9.460940580000001</v>
+        <v>9.416893512</v>
       </c>
       <c r="Q67">
-        <v>20.16094058</v>
+        <v>20.116893512</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1231643110077595</v>
+        <v>0.1252352892007053</v>
       </c>
       <c r="T67">
-        <v>1.304473426831777</v>
+        <v>1.339393094376865</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.304486282719204</v>
+        <v>4.239266793587095</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07233543832823978</v>
+        <v>0.07225876780376374</v>
       </c>
       <c r="C68">
-        <v>38.38422190005139</v>
+        <v>37.50228456150572</v>
       </c>
       <c r="D68">
-        <v>71.96622190005139</v>
+        <v>72.06128456150573</v>
       </c>
       <c r="E68">
-        <v>46.582</v>
+        <v>47.559</v>
       </c>
       <c r="F68">
-        <v>64.482</v>
+        <v>65.459</v>
       </c>
       <c r="G68">
         <v>30.9</v>
@@ -6863,28 +6863,28 @@
         <v>15.8</v>
       </c>
       <c r="M68">
-        <v>3.7270596</v>
+        <v>3.7835302</v>
       </c>
       <c r="N68">
-        <v>12.0729404</v>
+        <v>12.0164698</v>
       </c>
       <c r="O68">
-        <v>2.656046888</v>
+        <v>2.643623356</v>
       </c>
       <c r="P68">
-        <v>9.416893512</v>
+        <v>9.372846444</v>
       </c>
       <c r="Q68">
-        <v>20.116893512</v>
+        <v>20.072846444</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1252352892007053</v>
+        <v>0.1274317812235265</v>
       </c>
       <c r="T68">
-        <v>1.339393094376865</v>
+        <v>1.376429105409535</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.239266793587095</v>
+        <v>4.17599415487684</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07225876780376374</v>
+        <v>0.07218209727928769</v>
       </c>
       <c r="C69">
-        <v>37.50228456150572</v>
+        <v>36.62059869823049</v>
       </c>
       <c r="D69">
-        <v>72.06128456150573</v>
+        <v>72.15659869823048</v>
       </c>
       <c r="E69">
-        <v>47.559</v>
+        <v>48.53599999999999</v>
       </c>
       <c r="F69">
-        <v>65.459</v>
+        <v>66.43599999999999</v>
       </c>
       <c r="G69">
         <v>30.9</v>
@@ -6945,28 +6945,28 @@
         <v>15.8</v>
       </c>
       <c r="M69">
-        <v>3.7835302</v>
+        <v>3.8400008</v>
       </c>
       <c r="N69">
-        <v>12.0164698</v>
+        <v>11.9599992</v>
       </c>
       <c r="O69">
-        <v>2.643623356</v>
+        <v>2.631199824</v>
       </c>
       <c r="P69">
-        <v>9.372846444</v>
+        <v>9.328799375999999</v>
       </c>
       <c r="Q69">
-        <v>20.072846444</v>
+        <v>20.028799376</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1274317812235265</v>
+        <v>0.129765553997774</v>
       </c>
       <c r="T69">
-        <v>1.376429105409535</v>
+        <v>1.415779867131746</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.17599415487684</v>
+        <v>4.114582476128652</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07218209727928769</v>
+        <v>0.07210542675481164</v>
       </c>
       <c r="C70">
-        <v>36.62059869823049</v>
+        <v>35.73916530941246</v>
       </c>
       <c r="D70">
-        <v>72.15659869823048</v>
+        <v>72.25216530941245</v>
       </c>
       <c r="E70">
-        <v>48.53599999999999</v>
+        <v>49.513</v>
       </c>
       <c r="F70">
-        <v>66.43599999999999</v>
+        <v>67.413</v>
       </c>
       <c r="G70">
         <v>30.9</v>
@@ -7027,28 +7027,28 @@
         <v>15.8</v>
       </c>
       <c r="M70">
-        <v>3.8400008</v>
+        <v>3.8964714</v>
       </c>
       <c r="N70">
-        <v>11.9599992</v>
+        <v>11.9035286</v>
       </c>
       <c r="O70">
-        <v>2.631199824</v>
+        <v>2.618776292</v>
       </c>
       <c r="P70">
-        <v>9.328799375999999</v>
+        <v>9.284752308000002</v>
       </c>
       <c r="Q70">
-        <v>20.028799376</v>
+        <v>19.984752308</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.129765553997774</v>
+        <v>0.1322498927574569</v>
       </c>
       <c r="T70">
-        <v>1.415779867131746</v>
+        <v>1.457669387674745</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.114582476128652</v>
+        <v>4.05495084603983</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07210542675481164</v>
+        <v>0.07393975623033558</v>
       </c>
       <c r="C71">
-        <v>35.73916530941246</v>
+        <v>32.54303903245501</v>
       </c>
       <c r="D71">
-        <v>72.25216530941245</v>
+        <v>70.03303903245502</v>
       </c>
       <c r="E71">
-        <v>49.513</v>
+        <v>50.49</v>
       </c>
       <c r="F71">
-        <v>67.413</v>
+        <v>68.39</v>
       </c>
       <c r="G71">
         <v>30.9</v>
@@ -7109,45 +7109,45 @@
         <v>15.8</v>
       </c>
       <c r="M71">
-        <v>3.8964714</v>
+        <v>4.192307</v>
       </c>
       <c r="N71">
-        <v>11.9035286</v>
+        <v>11.607693</v>
       </c>
       <c r="O71">
-        <v>2.618776292</v>
+        <v>2.55369246</v>
       </c>
       <c r="P71">
-        <v>9.284752308000002</v>
+        <v>9.054000540000001</v>
       </c>
       <c r="Q71">
-        <v>19.984752308</v>
+        <v>19.75400054</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1322498927574569</v>
+        <v>0.1348998541011186</v>
       </c>
       <c r="T71">
-        <v>1.457669387674745</v>
+        <v>1.502351542920611</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.05495084603983</v>
+        <v>3.768807961821498</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07393975623033558</v>
+        <v>0.07389038570585954</v>
       </c>
       <c r="C72">
-        <v>32.54303903245501</v>
+        <v>31.62397972418798</v>
       </c>
       <c r="D72">
-        <v>70.03303903245502</v>
+        <v>70.09097972418799</v>
       </c>
       <c r="E72">
-        <v>50.49</v>
+        <v>51.46700000000001</v>
       </c>
       <c r="F72">
-        <v>68.39</v>
+        <v>69.367</v>
       </c>
       <c r="G72">
         <v>30.9</v>
@@ -7191,28 +7191,28 @@
         <v>15.8</v>
       </c>
       <c r="M72">
-        <v>4.192307</v>
+        <v>4.2521971</v>
       </c>
       <c r="N72">
-        <v>11.607693</v>
+        <v>11.5478029</v>
       </c>
       <c r="O72">
-        <v>2.55369246</v>
+        <v>2.540516638</v>
       </c>
       <c r="P72">
-        <v>9.054000540000001</v>
+        <v>9.007286262000001</v>
       </c>
       <c r="Q72">
-        <v>19.75400054</v>
+        <v>19.707286262</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1348998541011186</v>
+        <v>0.1377325713995157</v>
       </c>
       <c r="T72">
-        <v>1.502351542920611</v>
+        <v>1.550115226114468</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.768807961821498</v>
+        <v>3.715726159542323</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07389038570585954</v>
+        <v>0.07384101518138349</v>
       </c>
       <c r="C73">
-        <v>31.62397972418799</v>
+        <v>30.70501636787642</v>
       </c>
       <c r="D73">
-        <v>70.09097972418799</v>
+        <v>70.14901636787641</v>
       </c>
       <c r="E73">
-        <v>51.46699999999999</v>
+        <v>52.444</v>
       </c>
       <c r="F73">
-        <v>69.36699999999999</v>
+        <v>70.34399999999999</v>
       </c>
       <c r="G73">
         <v>30.9</v>
@@ -7273,28 +7273,28 @@
         <v>15.8</v>
       </c>
       <c r="M73">
-        <v>4.252197099999999</v>
+        <v>4.3120872</v>
       </c>
       <c r="N73">
-        <v>11.5478029</v>
+        <v>11.4879128</v>
       </c>
       <c r="O73">
-        <v>2.540516638</v>
+        <v>2.527340816</v>
       </c>
       <c r="P73">
-        <v>9.007286262000001</v>
+        <v>8.960571984</v>
       </c>
       <c r="Q73">
-        <v>19.707286262</v>
+        <v>19.660571984</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1377325713995156</v>
+        <v>0.1407676256477982</v>
       </c>
       <c r="T73">
-        <v>1.550115226114467</v>
+        <v>1.601290600965028</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.715726159542323</v>
+        <v>3.664118851770901</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07384101518138349</v>
+        <v>0.07379164465690743</v>
       </c>
       <c r="C74">
-        <v>30.70501636787642</v>
+        <v>29.78614920206785</v>
       </c>
       <c r="D74">
-        <v>70.14901636787641</v>
+        <v>70.20714920206782</v>
       </c>
       <c r="E74">
-        <v>52.444</v>
+        <v>53.42099999999999</v>
       </c>
       <c r="F74">
-        <v>70.34399999999999</v>
+        <v>71.32099999999998</v>
       </c>
       <c r="G74">
         <v>30.9</v>
@@ -7355,28 +7355,28 @@
         <v>15.8</v>
       </c>
       <c r="M74">
-        <v>4.3120872</v>
+        <v>4.371977299999999</v>
       </c>
       <c r="N74">
-        <v>11.4879128</v>
+        <v>11.4280227</v>
       </c>
       <c r="O74">
-        <v>2.527340816</v>
+        <v>2.514164994</v>
       </c>
       <c r="P74">
-        <v>8.960571984</v>
+        <v>8.913857706000002</v>
       </c>
       <c r="Q74">
-        <v>19.660571984</v>
+        <v>19.613857706</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1407676256477982</v>
+        <v>0.1440274987292868</v>
       </c>
       <c r="T74">
-        <v>1.601290600965028</v>
+        <v>1.656256744323037</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.664118851770901</v>
+        <v>3.613925442842533</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07379164465690743</v>
+        <v>0.07374227413243138</v>
       </c>
       <c r="C75">
-        <v>29.78614920206785</v>
+        <v>28.86737846610121</v>
       </c>
       <c r="D75">
-        <v>70.20714920206782</v>
+        <v>70.2653784661012</v>
       </c>
       <c r="E75">
-        <v>53.42099999999999</v>
+        <v>54.39799999999999</v>
       </c>
       <c r="F75">
-        <v>71.32099999999998</v>
+        <v>72.29799999999999</v>
       </c>
       <c r="G75">
         <v>30.9</v>
@@ -7437,28 +7437,28 @@
         <v>15.8</v>
       </c>
       <c r="M75">
-        <v>4.371977299999999</v>
+        <v>4.431867399999999</v>
       </c>
       <c r="N75">
-        <v>11.4280227</v>
+        <v>11.3681326</v>
       </c>
       <c r="O75">
-        <v>2.514164994</v>
+        <v>2.500989172000001</v>
       </c>
       <c r="P75">
-        <v>8.913857706000002</v>
+        <v>8.867143428000002</v>
       </c>
       <c r="Q75">
-        <v>19.613857706</v>
+        <v>19.567143428</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1440274987292868</v>
+        <v>0.1475381312785822</v>
       </c>
       <c r="T75">
-        <v>1.656256744323037</v>
+        <v>1.71545105255474</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.613925442842533</v>
+        <v>3.565088612533851</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07374227413243138</v>
+        <v>0.07369290360795533</v>
       </c>
       <c r="C76">
-        <v>28.86737846610121</v>
+        <v>27.9487044001102</v>
       </c>
       <c r="D76">
-        <v>70.2653784661012</v>
+        <v>70.3237044001102</v>
       </c>
       <c r="E76">
-        <v>54.39799999999999</v>
+        <v>55.37499999999999</v>
       </c>
       <c r="F76">
-        <v>72.29799999999999</v>
+        <v>73.27499999999999</v>
       </c>
       <c r="G76">
         <v>30.9</v>
@@ -7519,28 +7519,28 @@
         <v>15.8</v>
       </c>
       <c r="M76">
-        <v>4.431867399999999</v>
+        <v>4.491757499999999</v>
       </c>
       <c r="N76">
-        <v>11.3681326</v>
+        <v>11.3082425</v>
       </c>
       <c r="O76">
-        <v>2.500989172000001</v>
+        <v>2.487813350000001</v>
       </c>
       <c r="P76">
-        <v>8.867143428000002</v>
+        <v>8.820429150000002</v>
       </c>
       <c r="Q76">
-        <v>19.567143428</v>
+        <v>19.52042915</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1475381312785822</v>
+        <v>0.1513296144318213</v>
       </c>
       <c r="T76">
-        <v>1.71545105255474</v>
+        <v>1.779380905444979</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.565088612533851</v>
+        <v>3.517554097700066</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07369290360795533</v>
+        <v>0.07530337308347929</v>
       </c>
       <c r="C77">
-        <v>27.9487044001102</v>
+        <v>25.11773020196343</v>
       </c>
       <c r="D77">
-        <v>70.3237044001102</v>
+        <v>68.46973020196342</v>
       </c>
       <c r="E77">
-        <v>55.37499999999999</v>
+        <v>56.352</v>
       </c>
       <c r="F77">
-        <v>73.27499999999999</v>
+        <v>74.252</v>
       </c>
       <c r="G77">
         <v>30.9</v>
@@ -7601,45 +7601,45 @@
         <v>15.8</v>
       </c>
       <c r="M77">
-        <v>4.491757499999999</v>
+        <v>4.7595532</v>
       </c>
       <c r="N77">
-        <v>11.3082425</v>
+        <v>11.0404468</v>
       </c>
       <c r="O77">
-        <v>2.487813350000001</v>
+        <v>2.428898296</v>
       </c>
       <c r="P77">
-        <v>8.820429150000002</v>
+        <v>8.611548504000002</v>
       </c>
       <c r="Q77">
-        <v>19.52042915</v>
+        <v>19.311548504</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1513296144318213</v>
+        <v>0.155437054514497</v>
       </c>
       <c r="T77">
-        <v>1.779380905444979</v>
+        <v>1.848638246076071</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.517554097700066</v>
+        <v>3.319639330851476</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07530337308347929</v>
+        <v>0.07527584255900324</v>
       </c>
       <c r="C78">
-        <v>25.11773020196343</v>
+        <v>24.17160174377834</v>
       </c>
       <c r="D78">
-        <v>68.46973020196342</v>
+        <v>68.50060174377833</v>
       </c>
       <c r="E78">
-        <v>56.352</v>
+        <v>57.329</v>
       </c>
       <c r="F78">
-        <v>74.252</v>
+        <v>75.229</v>
       </c>
       <c r="G78">
         <v>30.9</v>
@@ -7683,28 +7683,28 @@
         <v>15.8</v>
       </c>
       <c r="M78">
-        <v>4.7595532</v>
+        <v>4.8221789</v>
       </c>
       <c r="N78">
-        <v>11.0404468</v>
+        <v>10.9778211</v>
       </c>
       <c r="O78">
-        <v>2.428898296</v>
+        <v>2.415120642</v>
       </c>
       <c r="P78">
-        <v>8.611548504000002</v>
+        <v>8.562700458</v>
       </c>
       <c r="Q78">
-        <v>19.311548504</v>
+        <v>19.262700458</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.155437054514497</v>
+        <v>0.1599016633000141</v>
       </c>
       <c r="T78">
-        <v>1.848638246076071</v>
+        <v>1.923917964153345</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.319639330851476</v>
+        <v>3.276527131749508</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07527584255900324</v>
+        <v>0.0752483120345272</v>
       </c>
       <c r="C79">
-        <v>24.17160174377834</v>
+        <v>23.22550113679105</v>
       </c>
       <c r="D79">
-        <v>68.50060174377833</v>
+        <v>68.53150113679104</v>
       </c>
       <c r="E79">
-        <v>57.329</v>
+        <v>58.30599999999999</v>
       </c>
       <c r="F79">
-        <v>75.229</v>
+        <v>76.20599999999999</v>
       </c>
       <c r="G79">
         <v>30.9</v>
@@ -7765,28 +7765,28 @@
         <v>15.8</v>
       </c>
       <c r="M79">
-        <v>4.8221789</v>
+        <v>4.8848046</v>
       </c>
       <c r="N79">
-        <v>10.9778211</v>
+        <v>10.9151954</v>
       </c>
       <c r="O79">
-        <v>2.415120642</v>
+        <v>2.401342988000001</v>
       </c>
       <c r="P79">
-        <v>8.562700458</v>
+        <v>8.513852412000002</v>
       </c>
       <c r="Q79">
-        <v>19.262700458</v>
+        <v>19.213852412</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1599016633000141</v>
+        <v>0.1647721456114872</v>
       </c>
       <c r="T79">
-        <v>1.923917964153345</v>
+        <v>2.006041292964917</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.276527131749508</v>
+        <v>3.234520373650156</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0752483120345272</v>
+        <v>0.07522078151005113</v>
       </c>
       <c r="C80">
-        <v>23.22550113679105</v>
+        <v>22.27942841870808</v>
       </c>
       <c r="D80">
-        <v>68.53150113679104</v>
+        <v>68.56242841870808</v>
       </c>
       <c r="E80">
-        <v>58.30599999999999</v>
+        <v>59.28299999999999</v>
       </c>
       <c r="F80">
-        <v>76.20599999999999</v>
+        <v>77.18299999999999</v>
       </c>
       <c r="G80">
         <v>30.9</v>
@@ -7847,28 +7847,28 @@
         <v>15.8</v>
       </c>
       <c r="M80">
-        <v>4.8848046</v>
+        <v>4.9474303</v>
       </c>
       <c r="N80">
-        <v>10.9151954</v>
+        <v>10.8525697</v>
       </c>
       <c r="O80">
-        <v>2.401342988000001</v>
+        <v>2.387565334</v>
       </c>
       <c r="P80">
-        <v>8.513852412000002</v>
+        <v>8.465004366000001</v>
       </c>
       <c r="Q80">
-        <v>19.213852412</v>
+        <v>19.165004366</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1647721456114872</v>
+        <v>0.1701064833811959</v>
       </c>
       <c r="T80">
-        <v>2.006041292964917</v>
+        <v>2.095985891187114</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.234520373650156</v>
+        <v>3.193577077781167</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07522078151005113</v>
+        <v>0.07519325098557508</v>
       </c>
       <c r="C81">
-        <v>22.27942841870808</v>
+        <v>21.33338362730402</v>
       </c>
       <c r="D81">
-        <v>68.56242841870808</v>
+        <v>68.59338362730402</v>
       </c>
       <c r="E81">
-        <v>59.28299999999999</v>
+        <v>60.26</v>
       </c>
       <c r="F81">
-        <v>77.18299999999999</v>
+        <v>78.16</v>
       </c>
       <c r="G81">
         <v>30.9</v>
@@ -7929,28 +7929,28 @@
         <v>15.8</v>
       </c>
       <c r="M81">
-        <v>4.9474303</v>
+        <v>5.010056000000001</v>
       </c>
       <c r="N81">
-        <v>10.8525697</v>
+        <v>10.789944</v>
       </c>
       <c r="O81">
-        <v>2.387565334</v>
+        <v>2.37378768</v>
       </c>
       <c r="P81">
-        <v>8.465004366000001</v>
+        <v>8.416156320000001</v>
       </c>
       <c r="Q81">
-        <v>19.165004366</v>
+        <v>19.11615632</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1701064833811959</v>
+        <v>0.1759742549278754</v>
       </c>
       <c r="T81">
-        <v>2.095985891187114</v>
+        <v>2.194924949231531</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.193577077781167</v>
+        <v>3.153657364308902</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07519325098557508</v>
+        <v>0.07516572046109904</v>
       </c>
       <c r="C82">
-        <v>21.33338362730402</v>
+        <v>20.3873668004218</v>
       </c>
       <c r="D82">
-        <v>68.59338362730402</v>
+        <v>68.6243668004218</v>
       </c>
       <c r="E82">
-        <v>60.26</v>
+        <v>61.237</v>
       </c>
       <c r="F82">
-        <v>78.16</v>
+        <v>79.137</v>
       </c>
       <c r="G82">
         <v>30.9</v>
@@ -8011,28 +8011,28 @@
         <v>15.8</v>
       </c>
       <c r="M82">
-        <v>5.010056000000001</v>
+        <v>5.0726817</v>
       </c>
       <c r="N82">
-        <v>10.789944</v>
+        <v>10.7273183</v>
       </c>
       <c r="O82">
-        <v>2.37378768</v>
+        <v>2.360010026</v>
       </c>
       <c r="P82">
-        <v>8.416156320000001</v>
+        <v>8.367308274000001</v>
       </c>
       <c r="Q82">
-        <v>19.11615632</v>
+        <v>19.067308274</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1759742549278754</v>
+        <v>0.1824596866373634</v>
       </c>
       <c r="T82">
-        <v>2.194924949231531</v>
+        <v>2.304278644964834</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.153657364308902</v>
+        <v>3.114723322774224</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07516572046109904</v>
+        <v>0.075138189936623</v>
       </c>
       <c r="C83">
-        <v>20.3873668004218</v>
+        <v>19.44137797597271</v>
       </c>
       <c r="D83">
-        <v>68.6243668004218</v>
+        <v>68.6553779759727</v>
       </c>
       <c r="E83">
-        <v>61.237</v>
+        <v>62.21399999999999</v>
       </c>
       <c r="F83">
-        <v>79.137</v>
+        <v>80.11399999999999</v>
       </c>
       <c r="G83">
         <v>30.9</v>
@@ -8093,28 +8093,28 @@
         <v>15.8</v>
       </c>
       <c r="M83">
-        <v>5.0726817</v>
+        <v>5.135307399999999</v>
       </c>
       <c r="N83">
-        <v>10.7273183</v>
+        <v>10.6646926</v>
       </c>
       <c r="O83">
-        <v>2.360010026</v>
+        <v>2.346232372000001</v>
       </c>
       <c r="P83">
-        <v>8.367308274000001</v>
+        <v>8.318460228000001</v>
       </c>
       <c r="Q83">
-        <v>19.067308274</v>
+        <v>19.018460228</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1824596866373634</v>
+        <v>0.1896657218701277</v>
       </c>
       <c r="T83">
-        <v>2.304278644964834</v>
+        <v>2.425782751335171</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.114723322774224</v>
+        <v>3.076738892008685</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.075138189936623</v>
+        <v>0.07511065941214694</v>
       </c>
       <c r="C84">
-        <v>19.44137797597271</v>
+        <v>18.49541719193657</v>
       </c>
       <c r="D84">
-        <v>68.6553779759727</v>
+        <v>68.68641719193656</v>
       </c>
       <c r="E84">
-        <v>62.21399999999999</v>
+        <v>63.191</v>
       </c>
       <c r="F84">
-        <v>80.11399999999999</v>
+        <v>81.09099999999999</v>
       </c>
       <c r="G84">
         <v>30.9</v>
@@ -8175,28 +8175,28 @@
         <v>15.8</v>
       </c>
       <c r="M84">
-        <v>5.135307399999999</v>
+        <v>5.1979331</v>
       </c>
       <c r="N84">
-        <v>10.6646926</v>
+        <v>10.6020669</v>
       </c>
       <c r="O84">
-        <v>2.346232372000001</v>
+        <v>2.332454718</v>
       </c>
       <c r="P84">
-        <v>8.318460228000001</v>
+        <v>8.269612181999999</v>
       </c>
       <c r="Q84">
-        <v>19.018460228</v>
+        <v>18.969612182</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1896657218701277</v>
+        <v>0.1977195259538055</v>
       </c>
       <c r="T84">
-        <v>2.425782751335171</v>
+        <v>2.56158145845496</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.076738892008685</v>
+        <v>3.039669748731472</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07511065941214694</v>
+        <v>0.07508312888767089</v>
       </c>
       <c r="C85">
-        <v>18.49541719193657</v>
+        <v>17.54948448636195</v>
       </c>
       <c r="D85">
-        <v>68.68641719193656</v>
+        <v>68.71748448636194</v>
       </c>
       <c r="E85">
-        <v>63.191</v>
+        <v>64.16800000000001</v>
       </c>
       <c r="F85">
-        <v>81.09099999999999</v>
+        <v>82.068</v>
       </c>
       <c r="G85">
         <v>30.9</v>
@@ -8257,28 +8257,28 @@
         <v>15.8</v>
       </c>
       <c r="M85">
-        <v>5.1979331</v>
+        <v>5.2605588</v>
       </c>
       <c r="N85">
-        <v>10.6020669</v>
+        <v>10.5394412</v>
       </c>
       <c r="O85">
-        <v>2.332454718</v>
+        <v>2.318677064</v>
       </c>
       <c r="P85">
-        <v>8.269612181999999</v>
+        <v>8.220764136</v>
       </c>
       <c r="Q85">
-        <v>18.969612182</v>
+        <v>18.920764136</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1977195259538055</v>
+        <v>0.2067800555479431</v>
       </c>
       <c r="T85">
-        <v>2.56158145845496</v>
+        <v>2.714355003964722</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.039669748731472</v>
+        <v>3.003483204103716</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07508312888767089</v>
+        <v>0.08022699836319484</v>
       </c>
       <c r="C86">
-        <v>17.54948448636196</v>
+        <v>11.21770337343925</v>
       </c>
       <c r="D86">
-        <v>68.71748448636194</v>
+        <v>63.36270337343924</v>
       </c>
       <c r="E86">
-        <v>64.16799999999998</v>
+        <v>65.14499999999998</v>
       </c>
       <c r="F86">
-        <v>82.06799999999998</v>
+        <v>83.04499999999999</v>
       </c>
       <c r="G86">
         <v>30.9</v>
@@ -8339,45 +8339,45 @@
         <v>15.8</v>
       </c>
       <c r="M86">
-        <v>5.260558799999999</v>
+        <v>5.9709355</v>
       </c>
       <c r="N86">
-        <v>10.5394412</v>
+        <v>9.829064500000001</v>
       </c>
       <c r="O86">
-        <v>2.318677064000001</v>
+        <v>2.16239419</v>
       </c>
       <c r="P86">
-        <v>8.220764136000001</v>
+        <v>7.666670310000001</v>
       </c>
       <c r="Q86">
-        <v>18.920764136</v>
+        <v>18.36667031</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.206780055547943</v>
+        <v>0.2170486557546322</v>
       </c>
       <c r="T86">
-        <v>2.71435500396472</v>
+        <v>2.88749835554245</v>
       </c>
       <c r="U86">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.003483204103717</v>
+        <v>2.646151511768968</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08022699836319484</v>
+        <v>0.08026030783871879</v>
       </c>
       <c r="C87">
-        <v>11.21770337343925</v>
+        <v>10.20874630517832</v>
       </c>
       <c r="D87">
-        <v>63.36270337343924</v>
+        <v>63.33074630517831</v>
       </c>
       <c r="E87">
-        <v>65.14499999999998</v>
+        <v>66.12199999999999</v>
       </c>
       <c r="F87">
-        <v>83.04499999999999</v>
+        <v>84.02199999999999</v>
       </c>
       <c r="G87">
         <v>30.9</v>
@@ -8421,28 +8421,28 @@
         <v>15.8</v>
       </c>
       <c r="M87">
-        <v>5.9709355</v>
+        <v>6.041181799999999</v>
       </c>
       <c r="N87">
-        <v>9.829064500000001</v>
+        <v>9.7588182</v>
       </c>
       <c r="O87">
-        <v>2.16239419</v>
+        <v>2.146940004</v>
       </c>
       <c r="P87">
-        <v>7.666670310000001</v>
+        <v>7.611878196</v>
       </c>
       <c r="Q87">
-        <v>18.36667031</v>
+        <v>18.311878196</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2170486557546322</v>
+        <v>0.2287841988479913</v>
       </c>
       <c r="T87">
-        <v>2.88749835554245</v>
+        <v>3.085376471631284</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.646151511768968</v>
+        <v>2.615382308143748</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08026030783871879</v>
+        <v>0.08029361731424273</v>
       </c>
       <c r="C88">
-        <v>10.20874630517832</v>
+        <v>9.199821455852074</v>
       </c>
       <c r="D88">
-        <v>63.33074630517831</v>
+        <v>63.29882145585207</v>
       </c>
       <c r="E88">
-        <v>66.12199999999999</v>
+        <v>67.09899999999999</v>
       </c>
       <c r="F88">
-        <v>84.02199999999999</v>
+        <v>84.999</v>
       </c>
       <c r="G88">
         <v>30.9</v>
@@ -8503,28 +8503,28 @@
         <v>15.8</v>
       </c>
       <c r="M88">
-        <v>6.041181799999999</v>
+        <v>6.1114281</v>
       </c>
       <c r="N88">
-        <v>9.7588182</v>
+        <v>9.688571899999999</v>
       </c>
       <c r="O88">
-        <v>2.146940004</v>
+        <v>2.131485818</v>
       </c>
       <c r="P88">
-        <v>7.611878196</v>
+        <v>7.557086082</v>
       </c>
       <c r="Q88">
-        <v>18.311878196</v>
+        <v>18.257086082</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2287841988479913</v>
+        <v>0.2423252101095595</v>
       </c>
       <c r="T88">
-        <v>3.085376471631284</v>
+        <v>3.313697374810709</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.615382308143748</v>
+        <v>2.585320442532899</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08029361731424273</v>
+        <v>0.08032692678976669</v>
       </c>
       <c r="C89">
-        <v>9.199821455852074</v>
+        <v>8.190928776760614</v>
       </c>
       <c r="D89">
-        <v>63.29882145585207</v>
+        <v>63.2669287767606</v>
       </c>
       <c r="E89">
-        <v>67.09899999999999</v>
+        <v>68.07599999999999</v>
       </c>
       <c r="F89">
-        <v>84.999</v>
+        <v>85.97599999999998</v>
       </c>
       <c r="G89">
         <v>30.9</v>
@@ -8585,28 +8585,28 @@
         <v>15.8</v>
       </c>
       <c r="M89">
-        <v>6.1114281</v>
+        <v>6.181674399999999</v>
       </c>
       <c r="N89">
-        <v>9.688571899999999</v>
+        <v>9.618325600000002</v>
       </c>
       <c r="O89">
-        <v>2.131485818</v>
+        <v>2.116031632</v>
       </c>
       <c r="P89">
-        <v>7.557086082</v>
+        <v>7.502293968000002</v>
       </c>
       <c r="Q89">
-        <v>18.257086082</v>
+        <v>18.202293968</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2423252101095595</v>
+        <v>0.258123056581389</v>
       </c>
       <c r="T89">
-        <v>3.313697374810709</v>
+        <v>3.58007176185337</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.585320442532899</v>
+        <v>2.555941801140481</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08032692678976669</v>
+        <v>0.08036023626529064</v>
       </c>
       <c r="C90">
-        <v>8.190928776760614</v>
+        <v>7.182068219302195</v>
       </c>
       <c r="D90">
-        <v>63.2669287767606</v>
+        <v>63.23506821930219</v>
       </c>
       <c r="E90">
-        <v>68.07599999999999</v>
+        <v>69.053</v>
       </c>
       <c r="F90">
-        <v>85.97599999999998</v>
+        <v>86.95299999999999</v>
       </c>
       <c r="G90">
         <v>30.9</v>
@@ -8667,28 +8667,28 @@
         <v>15.8</v>
       </c>
       <c r="M90">
-        <v>6.181674399999999</v>
+        <v>6.251920699999999</v>
       </c>
       <c r="N90">
-        <v>9.618325600000002</v>
+        <v>9.548079300000001</v>
       </c>
       <c r="O90">
-        <v>2.116031632</v>
+        <v>2.100577446</v>
       </c>
       <c r="P90">
-        <v>7.502293968000002</v>
+        <v>7.447501854</v>
       </c>
       <c r="Q90">
-        <v>18.202293968</v>
+        <v>18.147501854</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.258123056581389</v>
+        <v>0.2767932387753694</v>
       </c>
       <c r="T90">
-        <v>3.58007176185337</v>
+        <v>3.894877855631061</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.555941801140481</v>
+        <v>2.527223353936655</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08036023626529064</v>
+        <v>0.0831313457408146</v>
       </c>
       <c r="C91">
-        <v>7.182068219302195</v>
+        <v>3.662359972978052</v>
       </c>
       <c r="D91">
-        <v>63.23506821930219</v>
+        <v>60.69235997297805</v>
       </c>
       <c r="E91">
-        <v>69.053</v>
+        <v>70.03</v>
       </c>
       <c r="F91">
-        <v>86.95299999999999</v>
+        <v>87.92999999999999</v>
       </c>
       <c r="G91">
         <v>30.9</v>
@@ -8749,45 +8749,45 @@
         <v>15.8</v>
       </c>
       <c r="M91">
-        <v>6.251920699999999</v>
+        <v>6.665094</v>
       </c>
       <c r="N91">
-        <v>9.548079300000001</v>
+        <v>9.134906000000001</v>
       </c>
       <c r="O91">
-        <v>2.100577446</v>
+        <v>2.00967932</v>
       </c>
       <c r="P91">
-        <v>7.447501854</v>
+        <v>7.125226680000001</v>
       </c>
       <c r="Q91">
-        <v>18.147501854</v>
+        <v>17.82522668</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2767932387753694</v>
+        <v>0.2991974574081459</v>
       </c>
       <c r="T91">
-        <v>3.894877855631061</v>
+        <v>4.272645168164291</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.527223353936655</v>
+        <v>2.370559214918799</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0831313457408146</v>
+        <v>0.08319507521633854</v>
       </c>
       <c r="C92">
-        <v>3.662359972978052</v>
+        <v>2.62928645589686</v>
       </c>
       <c r="D92">
-        <v>60.69235997297805</v>
+        <v>60.63628645589687</v>
       </c>
       <c r="E92">
-        <v>70.03</v>
+        <v>71.00700000000001</v>
       </c>
       <c r="F92">
-        <v>87.92999999999999</v>
+        <v>88.907</v>
       </c>
       <c r="G92">
         <v>30.9</v>
@@ -8831,28 +8831,28 @@
         <v>15.8</v>
       </c>
       <c r="M92">
-        <v>6.665094</v>
+        <v>6.7391506</v>
       </c>
       <c r="N92">
-        <v>9.134906000000001</v>
+        <v>9.0608494</v>
       </c>
       <c r="O92">
-        <v>2.00967932</v>
+        <v>1.993386868</v>
       </c>
       <c r="P92">
-        <v>7.125226680000001</v>
+        <v>7.067462532</v>
       </c>
       <c r="Q92">
-        <v>17.82522668</v>
+        <v>17.767462532</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2991974574081459</v>
+        <v>0.3265803912926505</v>
       </c>
       <c r="T92">
-        <v>4.272645168164291</v>
+        <v>4.734360772371572</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.370559214918799</v>
+        <v>2.344509113655955</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08319507521633854</v>
+        <v>0.08325880469186249</v>
       </c>
       <c r="C93">
-        <v>2.62928645589686</v>
+        <v>1.596316455536581</v>
       </c>
       <c r="D93">
-        <v>60.63628645589687</v>
+        <v>60.58031645553658</v>
       </c>
       <c r="E93">
-        <v>71.00700000000001</v>
+        <v>71.98400000000001</v>
       </c>
       <c r="F93">
-        <v>88.907</v>
+        <v>89.884</v>
       </c>
       <c r="G93">
         <v>30.9</v>
@@ -8913,28 +8913,28 @@
         <v>15.8</v>
       </c>
       <c r="M93">
-        <v>6.7391506</v>
+        <v>6.813207200000001</v>
       </c>
       <c r="N93">
-        <v>9.0608494</v>
+        <v>8.9867928</v>
       </c>
       <c r="O93">
-        <v>1.993386868</v>
+        <v>1.977094416</v>
       </c>
       <c r="P93">
-        <v>7.067462532</v>
+        <v>7.009698384</v>
       </c>
       <c r="Q93">
-        <v>17.767462532</v>
+        <v>17.709698384</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3265803912926505</v>
+        <v>0.3608090586482812</v>
       </c>
       <c r="T93">
-        <v>4.734360772371572</v>
+        <v>5.311505277630673</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.344509113655955</v>
+        <v>2.319025318942304</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08325880469186249</v>
+        <v>0.08332253416738644</v>
       </c>
       <c r="C94">
-        <v>1.596316455536581</v>
+        <v>0.5634496855098945</v>
       </c>
       <c r="D94">
-        <v>60.58031645553658</v>
+        <v>60.52444968550989</v>
       </c>
       <c r="E94">
-        <v>71.98400000000001</v>
+        <v>72.96099999999998</v>
       </c>
       <c r="F94">
-        <v>89.884</v>
+        <v>90.86099999999999</v>
       </c>
       <c r="G94">
         <v>30.9</v>
@@ -8995,28 +8995,28 @@
         <v>15.8</v>
       </c>
       <c r="M94">
-        <v>6.813207200000001</v>
+        <v>6.887263799999999</v>
       </c>
       <c r="N94">
-        <v>8.9867928</v>
+        <v>8.912736200000001</v>
       </c>
       <c r="O94">
-        <v>1.977094416</v>
+        <v>1.960801964</v>
       </c>
       <c r="P94">
-        <v>7.009698384</v>
+        <v>6.951934236000001</v>
       </c>
       <c r="Q94">
-        <v>17.709698384</v>
+        <v>17.651934236</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3608090586482812</v>
+        <v>0.4048173452483779</v>
       </c>
       <c r="T94">
-        <v>5.311505277630673</v>
+        <v>6.053548212963802</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.319025318942304</v>
+        <v>2.294089562824645</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08332253416738644</v>
+        <v>0.08338626364291039</v>
       </c>
       <c r="C95">
-        <v>0.5634496855098945</v>
+        <v>-0.4693141395150775</v>
       </c>
       <c r="D95">
-        <v>60.52444968550989</v>
+        <v>60.46868586048492</v>
       </c>
       <c r="E95">
-        <v>72.96099999999998</v>
+        <v>73.93799999999999</v>
       </c>
       <c r="F95">
-        <v>90.86099999999999</v>
+        <v>91.83799999999999</v>
       </c>
       <c r="G95">
         <v>30.9</v>
@@ -9077,28 +9077,28 @@
         <v>15.8</v>
       </c>
       <c r="M95">
-        <v>6.887263799999999</v>
+        <v>6.9613204</v>
       </c>
       <c r="N95">
-        <v>8.912736200000001</v>
+        <v>8.838679600000001</v>
       </c>
       <c r="O95">
-        <v>1.960801964</v>
+        <v>1.944509512</v>
       </c>
       <c r="P95">
-        <v>6.951934236000001</v>
+        <v>6.894170088000001</v>
       </c>
       <c r="Q95">
-        <v>17.651934236</v>
+        <v>17.594170088</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4048173452483779</v>
+        <v>0.4634950607151734</v>
       </c>
       <c r="T95">
-        <v>6.053548212963802</v>
+        <v>7.042938793407976</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.294089562824645</v>
+        <v>2.269684354709489</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08338626364291039</v>
+        <v>0.08344999311843435</v>
       </c>
       <c r="C96">
-        <v>-0.4693141395150775</v>
+        <v>-1.50197530381962</v>
       </c>
       <c r="D96">
-        <v>60.46868586048492</v>
+        <v>60.41302469618038</v>
       </c>
       <c r="E96">
-        <v>73.93799999999999</v>
+        <v>74.91499999999999</v>
       </c>
       <c r="F96">
-        <v>91.83799999999999</v>
+        <v>92.815</v>
       </c>
       <c r="G96">
         <v>30.9</v>
@@ -9159,28 +9159,28 @@
         <v>15.8</v>
       </c>
       <c r="M96">
-        <v>6.9613204</v>
+        <v>7.035377</v>
       </c>
       <c r="N96">
-        <v>8.838679600000001</v>
+        <v>8.764623</v>
       </c>
       <c r="O96">
-        <v>1.944509512</v>
+        <v>1.92821706</v>
       </c>
       <c r="P96">
-        <v>6.894170088000001</v>
+        <v>6.836405940000001</v>
       </c>
       <c r="Q96">
-        <v>17.594170088</v>
+        <v>17.53640594</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4634950607151734</v>
+        <v>0.5456438623686873</v>
       </c>
       <c r="T96">
-        <v>7.042938793407976</v>
+        <v>8.428085606029821</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.269684354709489</v>
+        <v>2.245792940449389</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08344999311843435</v>
+        <v>0.08351372259395828</v>
       </c>
       <c r="C97">
-        <v>-1.50197530381962</v>
+        <v>-2.534534090639255</v>
       </c>
       <c r="D97">
-        <v>60.41302469618038</v>
+        <v>60.35746590936075</v>
       </c>
       <c r="E97">
-        <v>74.91499999999999</v>
+        <v>75.892</v>
       </c>
       <c r="F97">
-        <v>92.815</v>
+        <v>93.792</v>
       </c>
       <c r="G97">
         <v>30.9</v>
@@ -9241,28 +9241,28 @@
         <v>15.8</v>
       </c>
       <c r="M97">
-        <v>7.035377</v>
+        <v>7.109433600000001</v>
       </c>
       <c r="N97">
-        <v>8.764623</v>
+        <v>8.6905664</v>
       </c>
       <c r="O97">
-        <v>1.92821706</v>
+        <v>1.911924608</v>
       </c>
       <c r="P97">
-        <v>6.836405940000001</v>
+        <v>6.778641792</v>
       </c>
       <c r="Q97">
-        <v>17.53640594</v>
+        <v>17.478641792</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5456438623686873</v>
+        <v>0.6688670648489583</v>
       </c>
       <c r="T97">
-        <v>8.428085606029821</v>
+        <v>10.50580582496259</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.245792940449389</v>
+        <v>2.222399263986374</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0835137225939583</v>
+        <v>0.08357745206948225</v>
       </c>
       <c r="C98">
-        <v>-2.534534090639255</v>
+        <v>-3.566990782168588</v>
       </c>
       <c r="D98">
-        <v>60.35746590936073</v>
+        <v>60.30200921783141</v>
       </c>
       <c r="E98">
-        <v>75.892</v>
+        <v>76.869</v>
       </c>
       <c r="F98">
-        <v>93.79199999999999</v>
+        <v>94.76899999999999</v>
       </c>
       <c r="G98">
         <v>30.9</v>
@@ -9323,28 +9323,28 @@
         <v>15.8</v>
       </c>
       <c r="M98">
-        <v>7.1094336</v>
+        <v>7.1834902</v>
       </c>
       <c r="N98">
-        <v>8.690566400000002</v>
+        <v>8.616509800000001</v>
       </c>
       <c r="O98">
-        <v>1.911924608</v>
+        <v>1.895632156</v>
       </c>
       <c r="P98">
-        <v>6.778641792000001</v>
+        <v>6.720877644000001</v>
       </c>
       <c r="Q98">
-        <v>17.478641792</v>
+        <v>17.420877644</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6688670648489566</v>
+        <v>0.8742390689827404</v>
       </c>
       <c r="T98">
-        <v>10.50580582496256</v>
+        <v>13.96867285651716</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.222399263986374</v>
+        <v>2.199487931367958</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08357745206948225</v>
+        <v>0.0836411815450062</v>
       </c>
       <c r="C99">
-        <v>-3.566990782168588</v>
+        <v>-4.599345659565984</v>
       </c>
       <c r="D99">
-        <v>60.30200921783141</v>
+        <v>60.246654340434</v>
       </c>
       <c r="E99">
-        <v>76.869</v>
+        <v>77.84599999999998</v>
       </c>
       <c r="F99">
-        <v>94.76899999999999</v>
+        <v>95.74599999999998</v>
       </c>
       <c r="G99">
         <v>30.9</v>
@@ -9405,28 +9405,28 @@
         <v>15.8</v>
       </c>
       <c r="M99">
-        <v>7.1834902</v>
+        <v>7.257546799999999</v>
       </c>
       <c r="N99">
-        <v>8.616509800000001</v>
+        <v>8.542453200000001</v>
       </c>
       <c r="O99">
-        <v>1.895632156</v>
+        <v>1.879339704</v>
       </c>
       <c r="P99">
-        <v>6.720877644000001</v>
+        <v>6.663113496</v>
       </c>
       <c r="Q99">
-        <v>17.420877644</v>
+        <v>17.363113496</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8742390689827404</v>
+        <v>1.284983077250308</v>
       </c>
       <c r="T99">
-        <v>13.96867285651716</v>
+        <v>20.89440691962635</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.199487931367958</v>
+        <v>2.177044176966245</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0836411815450062</v>
+        <v>0.08370491102053014</v>
       </c>
       <c r="C100">
-        <v>-4.599345659565984</v>
+        <v>-5.631599002958467</v>
       </c>
       <c r="D100">
-        <v>60.246654340434</v>
+        <v>60.19140099704153</v>
       </c>
       <c r="E100">
-        <v>77.84599999999998</v>
+        <v>78.82299999999998</v>
       </c>
       <c r="F100">
-        <v>95.74599999999998</v>
+        <v>96.72299999999998</v>
       </c>
       <c r="G100">
         <v>30.9</v>
@@ -9487,28 +9487,28 @@
         <v>15.8</v>
       </c>
       <c r="M100">
-        <v>7.257546799999999</v>
+        <v>7.3316034</v>
       </c>
       <c r="N100">
-        <v>8.542453200000001</v>
+        <v>8.468396600000002</v>
       </c>
       <c r="O100">
-        <v>1.879339704</v>
+        <v>1.863047252000001</v>
       </c>
       <c r="P100">
-        <v>6.663113496</v>
+        <v>6.605349348000002</v>
       </c>
       <c r="Q100">
-        <v>17.363113496</v>
+        <v>17.305349348</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.284983077250308</v>
+        <v>2.517215102053011</v>
       </c>
       <c r="T100">
-        <v>20.89440691962635</v>
+        <v>41.67160910895393</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.177044176966245</v>
+        <v>2.155053831744363</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08370491102053014</v>
-      </c>
-      <c r="C101">
-        <v>-5.631599002958467</v>
-      </c>
-      <c r="D101">
-        <v>60.19140099704153</v>
-      </c>
-      <c r="E101">
-        <v>78.82299999999998</v>
-      </c>
-      <c r="F101">
-        <v>96.72299999999998</v>
-      </c>
-      <c r="G101">
-        <v>30.9</v>
-      </c>
-      <c r="H101">
-        <v>79.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>26.5</v>
-      </c>
-      <c r="K101">
-        <v>10.7</v>
-      </c>
-      <c r="L101">
-        <v>15.8</v>
-      </c>
-      <c r="M101">
-        <v>7.3316034</v>
-      </c>
-      <c r="N101">
-        <v>8.468396600000002</v>
-      </c>
-      <c r="O101">
-        <v>1.863047252000001</v>
-      </c>
-      <c r="P101">
-        <v>6.605349348000002</v>
-      </c>
-      <c r="Q101">
-        <v>17.305349348</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.517215102053011</v>
-      </c>
-      <c r="T101">
-        <v>41.67160910895393</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.155053831744363</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
